--- a/docs/CVAUP_TACHIRA.xlsx
+++ b/docs/CVAUP_TACHIRA.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marvin Tibaduiza\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\CVAUP-Reportes-App-WEB\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11065" uniqueCount="2328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11065" uniqueCount="2327">
   <si>
     <t>Estado</t>
   </si>
@@ -6370,9 +6370,6 @@
   </si>
   <si>
     <t>CUCHILLA DE ALMORZADERO</t>
-  </si>
-  <si>
-    <t>MP. ANTONIO ROMULO C</t>
   </si>
   <si>
     <t>CM. LAS MESAS</t>
@@ -7466,7 +7463,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.77734375" customWidth="1"/>
     <col min="3" max="3" width="30.5546875" customWidth="1"/>
     <col min="4" max="4" width="56.21875" customWidth="1"/>
     <col min="5" max="5" width="41.88671875" customWidth="1"/>
@@ -7540,7 +7537,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -7676,7 +7673,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
@@ -7727,7 +7724,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>5</v>
       </c>
@@ -7761,7 +7758,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
@@ -7863,7 +7860,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>5</v>
       </c>
@@ -7880,7 +7877,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>5</v>
       </c>
@@ -7999,7 +7996,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>5</v>
       </c>
@@ -8271,7 +8268,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>5</v>
       </c>
@@ -8356,7 +8353,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>5</v>
       </c>
@@ -8373,7 +8370,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>5</v>
       </c>
@@ -8492,7 +8489,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>5</v>
       </c>
@@ -8526,7 +8523,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>5</v>
       </c>
@@ -9019,7 +9016,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>5</v>
       </c>
@@ -9172,7 +9169,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>5</v>
       </c>
@@ -9325,7 +9322,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>5</v>
       </c>
@@ -9342,7 +9339,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>5</v>
       </c>
@@ -9410,7 +9407,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>5</v>
       </c>
@@ -9648,7 +9645,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>5</v>
       </c>
@@ -9767,7 +9764,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>5</v>
       </c>
@@ -9869,7 +9866,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>5</v>
       </c>
@@ -9971,7 +9968,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>5</v>
       </c>
@@ -9988,7 +9985,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>5</v>
       </c>
@@ -10022,7 +10019,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>5</v>
       </c>
@@ -10073,7 +10070,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>5</v>
       </c>
@@ -10090,7 +10087,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>5</v>
       </c>
@@ -10753,7 +10750,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>5</v>
       </c>
@@ -10787,7 +10784,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>5</v>
       </c>
@@ -10872,7 +10869,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>5</v>
       </c>
@@ -10991,7 +10988,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>5</v>
       </c>
@@ -11076,7 +11073,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>5</v>
       </c>
@@ -11297,7 +11294,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>5</v>
       </c>
@@ -11501,7 +11498,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
         <v>5</v>
       </c>
@@ -11569,7 +11566,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>5</v>
       </c>
@@ -11637,7 +11634,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
         <v>5</v>
       </c>
@@ -11909,7 +11906,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
         <v>5</v>
       </c>
@@ -11943,7 +11940,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
         <v>5</v>
       </c>
@@ -12079,7 +12076,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
         <v>5</v>
       </c>
@@ -12113,7 +12110,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
         <v>5</v>
       </c>
@@ -12215,7 +12212,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
         <v>5</v>
       </c>
@@ -12232,7 +12229,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
         <v>5</v>
       </c>
@@ -12368,7 +12365,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
         <v>5</v>
       </c>
@@ -12963,7 +12960,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
         <v>5</v>
       </c>
@@ -12997,7 +12994,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="s">
         <v>5</v>
       </c>
@@ -13286,7 +13283,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="s">
         <v>5</v>
       </c>
@@ -13371,7 +13368,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
         <v>5</v>
       </c>
@@ -13405,7 +13402,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
         <v>5</v>
       </c>
@@ -13473,7 +13470,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354" s="2" t="s">
         <v>5</v>
       </c>
@@ -13507,7 +13504,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
         <v>5</v>
       </c>
@@ -14102,7 +14099,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391" s="2" t="s">
         <v>5</v>
       </c>
@@ -14221,7 +14218,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
         <v>5</v>
       </c>
@@ -14255,7 +14252,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="s">
         <v>5</v>
       </c>
@@ -14272,7 +14269,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="s">
         <v>5</v>
       </c>
@@ -14323,7 +14320,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
         <v>5</v>
       </c>
@@ -14459,7 +14456,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="s">
         <v>5</v>
       </c>
@@ -14561,7 +14558,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A418" s="2" t="s">
         <v>5</v>
       </c>
@@ -14629,7 +14626,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A422" s="2" t="s">
         <v>5</v>
       </c>
@@ -14663,7 +14660,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A424" s="2" t="s">
         <v>5</v>
       </c>
@@ -14765,7 +14762,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="s">
         <v>5</v>
       </c>
@@ -14816,7 +14813,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A433" s="2" t="s">
         <v>5</v>
       </c>
@@ -14867,7 +14864,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436" s="2" t="s">
         <v>5</v>
       </c>
@@ -15003,7 +15000,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A444" s="2" t="s">
         <v>5</v>
       </c>
@@ -15054,7 +15051,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A447" s="2" t="s">
         <v>5</v>
       </c>
@@ -15088,7 +15085,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A449" s="2" t="s">
         <v>5</v>
       </c>
@@ -15173,7 +15170,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A454" s="2" t="s">
         <v>5</v>
       </c>
@@ -15190,7 +15187,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A455" s="2" t="s">
         <v>5</v>
       </c>
@@ -15513,7 +15510,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A474" s="2" t="s">
         <v>5</v>
       </c>
@@ -15598,7 +15595,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A479" s="2" t="s">
         <v>5</v>
       </c>
@@ -15921,7 +15918,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A498" s="2" t="s">
         <v>5</v>
       </c>
@@ -15938,7 +15935,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A499" s="2" t="s">
         <v>5</v>
       </c>
@@ -15955,7 +15952,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A500" s="2" t="s">
         <v>5</v>
       </c>
@@ -15972,7 +15969,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A501" s="2" t="s">
         <v>5</v>
       </c>
@@ -16159,7 +16156,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A512" s="2" t="s">
         <v>5</v>
       </c>
@@ -16346,7 +16343,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A523" s="2" t="s">
         <v>5</v>
       </c>
@@ -16499,7 +16496,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A532" s="2" t="s">
         <v>5</v>
       </c>
@@ -16771,7 +16768,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A548" s="2" t="s">
         <v>5</v>
       </c>
@@ -17298,7 +17295,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="579" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A579" s="2" t="s">
         <v>5</v>
       </c>
@@ -17536,7 +17533,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="593" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A593" s="2" t="s">
         <v>5</v>
       </c>
@@ -17655,7 +17652,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A600" s="2" t="s">
         <v>5</v>
       </c>
@@ -17978,7 +17975,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="619" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A619" s="2" t="s">
         <v>5</v>
       </c>
@@ -18148,7 +18145,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="629" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A629" s="2" t="s">
         <v>5</v>
       </c>
@@ -18216,7 +18213,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="633" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A633" s="2" t="s">
         <v>5</v>
       </c>
@@ -18233,7 +18230,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A634" s="2" t="s">
         <v>5</v>
       </c>
@@ -18284,7 +18281,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="637" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A637" s="2" t="s">
         <v>5</v>
       </c>
@@ -18318,7 +18315,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="639" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A639" s="2" t="s">
         <v>5</v>
       </c>
@@ -18335,7 +18332,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="640" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A640" s="2" t="s">
         <v>5</v>
       </c>
@@ -18352,7 +18349,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A641" s="2" t="s">
         <v>5</v>
       </c>
@@ -18369,7 +18366,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A642" s="2" t="s">
         <v>5</v>
       </c>
@@ -18420,7 +18417,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A645" s="2" t="s">
         <v>5</v>
       </c>
@@ -18437,7 +18434,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A646" s="2" t="s">
         <v>5</v>
       </c>
@@ -18590,7 +18587,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A655" s="2" t="s">
         <v>5</v>
       </c>
@@ -18692,7 +18689,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A661" s="2" t="s">
         <v>5</v>
       </c>
@@ -18896,7 +18893,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A673" s="2" t="s">
         <v>5</v>
       </c>
@@ -18964,7 +18961,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A677" s="2" t="s">
         <v>5</v>
       </c>
@@ -18981,7 +18978,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A678" s="2" t="s">
         <v>5</v>
       </c>
@@ -19066,7 +19063,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A683" s="2" t="s">
         <v>5</v>
       </c>
@@ -19117,7 +19114,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="686" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A686" s="2" t="s">
         <v>5</v>
       </c>
@@ -19134,7 +19131,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A687" s="2" t="s">
         <v>5</v>
       </c>
@@ -19185,7 +19182,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="690" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A690" s="2" t="s">
         <v>5</v>
       </c>
@@ -19202,7 +19199,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A691" s="2" t="s">
         <v>5</v>
       </c>
@@ -19219,7 +19216,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A692" s="2" t="s">
         <v>5</v>
       </c>
@@ -19576,7 +19573,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="713" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A713" s="2" t="s">
         <v>5</v>
       </c>
@@ -19593,7 +19590,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="714" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A714" s="2" t="s">
         <v>5</v>
       </c>
@@ -19644,7 +19641,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A717" s="2" t="s">
         <v>5</v>
       </c>
@@ -19814,7 +19811,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A727" s="2" t="s">
         <v>5</v>
       </c>
@@ -19831,7 +19828,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A728" s="2" t="s">
         <v>5</v>
       </c>
@@ -19848,7 +19845,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A729" s="2" t="s">
         <v>5</v>
       </c>
@@ -19967,7 +19964,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A736" s="2" t="s">
         <v>5</v>
       </c>
@@ -19984,7 +19981,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A737" s="2" t="s">
         <v>5</v>
       </c>
@@ -20001,7 +19998,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A738" s="2" t="s">
         <v>5</v>
       </c>
@@ -20086,7 +20083,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A743" s="2" t="s">
         <v>5</v>
       </c>
@@ -20120,7 +20117,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A745" s="2" t="s">
         <v>5</v>
       </c>
@@ -20137,7 +20134,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A746" s="2" t="s">
         <v>5</v>
       </c>
@@ -20154,7 +20151,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A747" s="2" t="s">
         <v>5</v>
       </c>
@@ -20205,7 +20202,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="750" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A750" s="2" t="s">
         <v>5</v>
       </c>
@@ -20222,7 +20219,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A751" s="2" t="s">
         <v>5</v>
       </c>
@@ -20239,7 +20236,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A752" s="2" t="s">
         <v>5</v>
       </c>
@@ -20358,7 +20355,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A759" s="2" t="s">
         <v>5</v>
       </c>
@@ -20409,7 +20406,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="762" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A762" s="2" t="s">
         <v>5</v>
       </c>
@@ -20426,7 +20423,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="763" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A763" s="2" t="s">
         <v>5</v>
       </c>
@@ -20460,7 +20457,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A765" s="2" t="s">
         <v>5</v>
       </c>
@@ -20477,7 +20474,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="766" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A766" s="2" t="s">
         <v>5</v>
       </c>
@@ -20494,7 +20491,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="767" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A767" s="2" t="s">
         <v>5</v>
       </c>
@@ -20630,7 +20627,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A775" s="2" t="s">
         <v>5</v>
       </c>
@@ -20664,7 +20661,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A777" s="2" t="s">
         <v>5</v>
       </c>
@@ -20698,7 +20695,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A779" s="2" t="s">
         <v>5</v>
       </c>
@@ -20800,7 +20797,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A785" s="2" t="s">
         <v>5</v>
       </c>
@@ -20902,7 +20899,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A791" s="2" t="s">
         <v>5</v>
       </c>
@@ -20936,7 +20933,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="793" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A793" s="2" t="s">
         <v>5</v>
       </c>
@@ -21072,7 +21069,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A801" s="2" t="s">
         <v>5</v>
       </c>
@@ -21174,7 +21171,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A807" s="2" t="s">
         <v>5</v>
       </c>
@@ -21242,7 +21239,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A811" s="2" t="s">
         <v>5</v>
       </c>
@@ -21293,7 +21290,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A814" s="2" t="s">
         <v>5</v>
       </c>
@@ -21429,7 +21426,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A822" s="2" t="s">
         <v>5</v>
       </c>
@@ -21480,7 +21477,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="825" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A825" s="2" t="s">
         <v>5</v>
       </c>
@@ -21582,7 +21579,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="831" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A831" s="2" t="s">
         <v>5</v>
       </c>
@@ -21718,7 +21715,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A839" s="2" t="s">
         <v>5</v>
       </c>
@@ -21735,7 +21732,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="840" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A840" s="2" t="s">
         <v>5</v>
       </c>
@@ -21752,7 +21749,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A841" s="2" t="s">
         <v>5</v>
       </c>
@@ -21854,7 +21851,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="847" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="847" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A847" s="2" t="s">
         <v>5</v>
       </c>
@@ -22041,7 +22038,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="858" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="858" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A858" s="2" t="s">
         <v>5</v>
       </c>
@@ -22058,7 +22055,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="859" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="859" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A859" s="2" t="s">
         <v>5</v>
       </c>
@@ -22126,7 +22123,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="863" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="863" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A863" s="2" t="s">
         <v>5</v>
       </c>
@@ -22330,7 +22327,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="875" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="875" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A875" s="2" t="s">
         <v>5</v>
       </c>
@@ -22347,7 +22344,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="876" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="876" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A876" s="2" t="s">
         <v>5</v>
       </c>
@@ -22432,7 +22429,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="881" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="881" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A881" s="2" t="s">
         <v>5</v>
       </c>
@@ -22534,7 +22531,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="887" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="887" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A887" s="2" t="s">
         <v>5</v>
       </c>
@@ -22636,7 +22633,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="893" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="893" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A893" s="2" t="s">
         <v>5</v>
       </c>
@@ -22670,7 +22667,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="895" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="895" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A895" s="2" t="s">
         <v>5</v>
       </c>
@@ -22704,7 +22701,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="897" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="897" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A897" s="2" t="s">
         <v>5</v>
       </c>
@@ -22789,7 +22786,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="902" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="902" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A902" s="2" t="s">
         <v>5</v>
       </c>
@@ -22806,7 +22803,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="903" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="903" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A903" s="2" t="s">
         <v>5</v>
       </c>
@@ -22823,7 +22820,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="904" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="904" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A904" s="2" t="s">
         <v>5</v>
       </c>
@@ -22840,7 +22837,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="905" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="905" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A905" s="2" t="s">
         <v>5</v>
       </c>
@@ -22857,7 +22854,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="906" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="906" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A906" s="2" t="s">
         <v>5</v>
       </c>
@@ -22993,7 +22990,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="914" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="914" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A914" s="2" t="s">
         <v>5</v>
       </c>
@@ -23027,7 +23024,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="916" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="916" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A916" s="2" t="s">
         <v>5</v>
       </c>
@@ -23095,7 +23092,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="920" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="920" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A920" s="2" t="s">
         <v>5</v>
       </c>
@@ -23112,7 +23109,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="921" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="921" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A921" s="2" t="s">
         <v>5</v>
       </c>
@@ -23180,7 +23177,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="925" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="925" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A925" s="2" t="s">
         <v>5</v>
       </c>
@@ -23197,7 +23194,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="926" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="926" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A926" s="2" t="s">
         <v>5</v>
       </c>
@@ -23214,7 +23211,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="927" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="927" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A927" s="2" t="s">
         <v>5</v>
       </c>
@@ -23231,7 +23228,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="928" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="928" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A928" s="2" t="s">
         <v>5</v>
       </c>
@@ -23248,7 +23245,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="929" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="929" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A929" s="2" t="s">
         <v>5</v>
       </c>
@@ -23350,7 +23347,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="935" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="935" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A935" s="2" t="s">
         <v>5</v>
       </c>
@@ -23367,7 +23364,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="936" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="936" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A936" s="2" t="s">
         <v>5</v>
       </c>
@@ -23639,7 +23636,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="952" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="952" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A952" s="2" t="s">
         <v>5</v>
       </c>
@@ -23656,7 +23653,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="953" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="953" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A953" s="2" t="s">
         <v>5</v>
       </c>
@@ -23707,7 +23704,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="956" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="956" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A956" s="2" t="s">
         <v>5</v>
       </c>
@@ -23741,7 +23738,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="958" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="958" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A958" s="2" t="s">
         <v>5</v>
       </c>
@@ -23758,7 +23755,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="959" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="959" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A959" s="2" t="s">
         <v>5</v>
       </c>
@@ -23775,7 +23772,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="960" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="960" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A960" s="2" t="s">
         <v>5</v>
       </c>
@@ -23860,7 +23857,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="965" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="965" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A965" s="2" t="s">
         <v>5</v>
       </c>
@@ -24047,7 +24044,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="976" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="976" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A976" s="2" t="s">
         <v>5</v>
       </c>
@@ -24166,7 +24163,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="983" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="983" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A983" s="2" t="s">
         <v>5</v>
       </c>
@@ -24251,7 +24248,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="988" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="988" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A988" s="2" t="s">
         <v>5</v>
       </c>
@@ -24353,7 +24350,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="994" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="994" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A994" s="2" t="s">
         <v>5</v>
       </c>
@@ -24489,7 +24486,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="1002" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1002" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1002" s="2" t="s">
         <v>5</v>
       </c>
@@ -24557,7 +24554,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="1006" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1006" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1006" s="2" t="s">
         <v>5</v>
       </c>
@@ -24727,7 +24724,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="1016" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1016" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1016" s="2" t="s">
         <v>5</v>
       </c>
@@ -24744,7 +24741,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="1017" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1017" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1017" s="2" t="s">
         <v>5</v>
       </c>
@@ -24948,7 +24945,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="1029" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1029" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1029" s="2" t="s">
         <v>5</v>
       </c>
@@ -24965,7 +24962,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="1030" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1030" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1030" s="2" t="s">
         <v>5</v>
       </c>
@@ -25135,7 +25132,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="1040" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1040" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1040" s="2" t="s">
         <v>5</v>
       </c>
@@ -25424,7 +25421,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="1057" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1057" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1057" s="2" t="s">
         <v>5</v>
       </c>
@@ -25611,7 +25608,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="1068" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1068" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1068" s="2" t="s">
         <v>5</v>
       </c>
@@ -25696,7 +25693,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="1073" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1073" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1073" s="2" t="s">
         <v>5</v>
       </c>
@@ -25730,7 +25727,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="1075" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1075" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1075" s="2" t="s">
         <v>5</v>
       </c>
@@ -25866,7 +25863,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="1083" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1083" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1083" s="2" t="s">
         <v>5</v>
       </c>
@@ -26410,7 +26407,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="1115" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1115" s="2" t="s">
         <v>5</v>
       </c>
@@ -26920,7 +26917,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="1145" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1145" s="2" t="s">
         <v>5</v>
       </c>
@@ -27549,7 +27546,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="1182" spans="1:5" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="1182" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1182" s="2" t="s">
         <v>5</v>
       </c>
@@ -27651,7 +27648,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="1188" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1188" s="2" t="s">
         <v>5</v>
       </c>
@@ -27668,7 +27665,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="1189" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1189" s="2" t="s">
         <v>5</v>
       </c>
@@ -27719,7 +27716,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="1192" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1192" s="2" t="s">
         <v>5</v>
       </c>
@@ -27838,7 +27835,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="1199" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1199" s="2" t="s">
         <v>5</v>
       </c>
@@ -27855,7 +27852,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="1200" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1200" s="2" t="s">
         <v>5</v>
       </c>
@@ -27923,7 +27920,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="1204" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1204" s="2" t="s">
         <v>5</v>
       </c>
@@ -27957,7 +27954,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="1206" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1206" s="2" t="s">
         <v>5</v>
       </c>
@@ -27991,7 +27988,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="1208" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1208" s="2" t="s">
         <v>5</v>
       </c>
@@ -28059,7 +28056,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="1212" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1212" s="2" t="s">
         <v>5</v>
       </c>
@@ -28093,7 +28090,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="1214" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1214" s="2" t="s">
         <v>5</v>
       </c>
@@ -28161,7 +28158,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="1218" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1218" s="2" t="s">
         <v>5</v>
       </c>
@@ -28280,7 +28277,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="1225" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1225" s="2" t="s">
         <v>5</v>
       </c>
@@ -28331,7 +28328,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1228" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="1228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1228" s="2" t="s">
         <v>5</v>
       </c>
@@ -28348,7 +28345,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="1229" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1229" s="2" t="s">
         <v>5</v>
       </c>
@@ -28399,7 +28396,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="1232" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1232" s="2" t="s">
         <v>5</v>
       </c>
@@ -28416,7 +28413,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="1233" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="1233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1233" s="2" t="s">
         <v>5</v>
       </c>
@@ -28518,7 +28515,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="1239" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1239" s="2" t="s">
         <v>5</v>
       </c>
@@ -28535,7 +28532,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="1240" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1240" s="2" t="s">
         <v>5</v>
       </c>
@@ -28552,7 +28549,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="1241" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1241" s="2" t="s">
         <v>5</v>
       </c>
@@ -28586,7 +28583,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="1243" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1243" s="2" t="s">
         <v>5</v>
       </c>
@@ -28705,7 +28702,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="1250" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1250" s="2" t="s">
         <v>5</v>
       </c>
@@ -28739,7 +28736,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="1252" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1252" s="2" t="s">
         <v>5</v>
       </c>
@@ -28756,7 +28753,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="1253" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1253" s="2" t="s">
         <v>5</v>
       </c>
@@ -28773,7 +28770,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="1254" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="1254" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1254" s="2" t="s">
         <v>5</v>
       </c>
@@ -28790,7 +28787,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="1255" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="1255" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1255" s="2" t="s">
         <v>5</v>
       </c>
@@ -28807,7 +28804,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="1256" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1256" s="2" t="s">
         <v>5</v>
       </c>
@@ -28841,7 +28838,7 @@
         <v>1396</v>
       </c>
     </row>
-    <row r="1258" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1258" s="2" t="s">
         <v>5</v>
       </c>
@@ -28909,7 +28906,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="1262" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1262" s="2" t="s">
         <v>5</v>
       </c>
@@ -28926,7 +28923,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="1263" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="1263" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1263" s="2" t="s">
         <v>5</v>
       </c>
@@ -28977,7 +28974,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="1266" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1266" s="2" t="s">
         <v>5</v>
       </c>
@@ -29011,7 +29008,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="1268" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1268" s="2" t="s">
         <v>5</v>
       </c>
@@ -29147,7 +29144,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="1276" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1276" s="2" t="s">
         <v>5</v>
       </c>
@@ -29487,7 +29484,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="1296" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1296" s="2" t="s">
         <v>5</v>
       </c>
@@ -29606,7 +29603,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="1303" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="1303" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1303" s="2" t="s">
         <v>5</v>
       </c>
@@ -29725,7 +29722,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="1310" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1310" s="2" t="s">
         <v>5</v>
       </c>
@@ -29810,7 +29807,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="1315" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1315" s="2" t="s">
         <v>5</v>
       </c>
@@ -29844,7 +29841,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="1317" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1317" s="2" t="s">
         <v>5</v>
       </c>
@@ -29895,7 +29892,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="1320" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1320" s="2" t="s">
         <v>5</v>
       </c>
@@ -29929,7 +29926,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="1322" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1322" s="2" t="s">
         <v>5</v>
       </c>
@@ -30405,7 +30402,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="1350" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1350" s="2" t="s">
         <v>5</v>
       </c>
@@ -30745,7 +30742,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="1370" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1370" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1370" s="2" t="s">
         <v>5</v>
       </c>
@@ -30847,7 +30844,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="1376" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1376" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1376" s="2" t="s">
         <v>5</v>
       </c>
@@ -31102,7 +31099,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="1391" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1391" s="2" t="s">
         <v>5</v>
       </c>
@@ -31323,7 +31320,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="1404" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1404" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1404" s="2" t="s">
         <v>5</v>
       </c>
@@ -31408,7 +31405,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="1409" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1409" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1409" s="2" t="s">
         <v>5</v>
       </c>
@@ -31425,7 +31422,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="1410" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1410" s="2" t="s">
         <v>5</v>
       </c>
@@ -31459,7 +31456,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="1412" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1412" s="2" t="s">
         <v>5</v>
       </c>
@@ -31527,7 +31524,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="1416" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1416" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1416" s="2" t="s">
         <v>5</v>
       </c>
@@ -31595,7 +31592,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="1420" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1420" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1420" s="2" t="s">
         <v>5</v>
       </c>
@@ -31612,7 +31609,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="1421" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1421" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1421" s="2" t="s">
         <v>5</v>
       </c>
@@ -31697,7 +31694,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="1426" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1426" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1426" s="2" t="s">
         <v>5</v>
       </c>
@@ -31714,7 +31711,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="1427" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1427" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1427" s="2" t="s">
         <v>5</v>
       </c>
@@ -31935,7 +31932,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="1440" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1440" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1440" s="2" t="s">
         <v>5</v>
       </c>
@@ -31952,7 +31949,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="1441" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1441" s="2" t="s">
         <v>5</v>
       </c>
@@ -32071,7 +32068,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="1448" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1448" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1448" s="2" t="s">
         <v>5</v>
       </c>
@@ -32105,7 +32102,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="1450" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1450" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1450" s="2" t="s">
         <v>5</v>
       </c>
@@ -32139,7 +32136,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="1452" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1452" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1452" s="2" t="s">
         <v>5</v>
       </c>
@@ -32156,7 +32153,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="1453" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1453" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1453" s="2" t="s">
         <v>5</v>
       </c>
@@ -32343,7 +32340,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="1464" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1464" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1464" s="2" t="s">
         <v>5</v>
       </c>
@@ -32496,7 +32493,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="1473" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1473" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1473" s="2" t="s">
         <v>5</v>
       </c>
@@ -32802,7 +32799,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="1491" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1491" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1491" s="2" t="s">
         <v>5</v>
       </c>
@@ -32853,7 +32850,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="1494" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1494" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1494" s="2" t="s">
         <v>5</v>
       </c>
@@ -32938,7 +32935,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="1499" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1499" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1499" s="2" t="s">
         <v>5</v>
       </c>
@@ -33023,7 +33020,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="1504" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1504" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1504" s="2" t="s">
         <v>5</v>
       </c>
@@ -33227,7 +33224,7 @@
         <v>1651</v>
       </c>
     </row>
-    <row r="1516" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1516" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1516" s="2" t="s">
         <v>5</v>
       </c>
@@ -33312,7 +33309,7 @@
         <v>1657</v>
       </c>
     </row>
-    <row r="1521" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1521" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1521" s="2" t="s">
         <v>5</v>
       </c>
@@ -33567,7 +33564,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="1536" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1536" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1536" s="2" t="s">
         <v>5</v>
       </c>
@@ -33856,7 +33853,7 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="1553" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="1553" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1553" s="2" t="s">
         <v>5</v>
       </c>
@@ -33958,7 +33955,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="1559" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="1559" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1559" s="2" t="s">
         <v>5</v>
       </c>
@@ -34043,7 +34040,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="1564" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1564" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1564" s="2" t="s">
         <v>5</v>
       </c>
@@ -34111,7 +34108,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="1568" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1568" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1568" s="2" t="s">
         <v>5</v>
       </c>
@@ -34128,7 +34125,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="1569" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1569" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1569" s="2" t="s">
         <v>5</v>
       </c>
@@ -34179,7 +34176,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="1572" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1572" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1572" s="2" t="s">
         <v>5</v>
       </c>
@@ -34230,7 +34227,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="1575" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1575" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1575" s="2" t="s">
         <v>5</v>
       </c>
@@ -34298,7 +34295,7 @@
         <v>1718</v>
       </c>
     </row>
-    <row r="1579" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1579" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1579" s="2" t="s">
         <v>5</v>
       </c>
@@ -34315,7 +34312,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="1580" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1580" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1580" s="2" t="s">
         <v>5</v>
       </c>
@@ -34434,7 +34431,7 @@
         <v>1726</v>
       </c>
     </row>
-    <row r="1587" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1587" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1587" s="2" t="s">
         <v>5</v>
       </c>
@@ -34519,7 +34516,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="1592" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1592" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1592" s="2" t="s">
         <v>5</v>
       </c>
@@ -34553,7 +34550,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="1594" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1594" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1594" s="2" t="s">
         <v>5</v>
       </c>
@@ -34672,7 +34669,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="1601" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="1601" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1601" s="2" t="s">
         <v>5</v>
       </c>
@@ -34723,7 +34720,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="1604" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1604" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1604" s="2" t="s">
         <v>5</v>
       </c>
@@ -34876,7 +34873,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="1613" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1613" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1613" s="2" t="s">
         <v>5</v>
       </c>
@@ -34893,7 +34890,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="1614" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1614" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1614" s="2" t="s">
         <v>5</v>
       </c>
@@ -34910,7 +34907,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="1615" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1615" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1615" s="2" t="s">
         <v>5</v>
       </c>
@@ -35046,7 +35043,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="1623" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1623" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1623" s="2" t="s">
         <v>5</v>
       </c>
@@ -35080,7 +35077,7 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="1625" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1625" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1625" s="2" t="s">
         <v>5</v>
       </c>
@@ -35216,7 +35213,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="1633" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1633" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1633" s="2" t="s">
         <v>5</v>
       </c>
@@ -35267,7 +35264,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="1636" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1636" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1636" s="2" t="s">
         <v>5</v>
       </c>
@@ -35301,7 +35298,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="1638" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1638" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1638" s="2" t="s">
         <v>5</v>
       </c>
@@ -35420,7 +35417,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="1645" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1645" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1645" s="2" t="s">
         <v>5</v>
       </c>
@@ -35573,7 +35570,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="1654" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1654" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1654" s="2" t="s">
         <v>5</v>
       </c>
@@ -35641,7 +35638,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="1658" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1658" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1658" s="2" t="s">
         <v>5</v>
       </c>
@@ -35947,7 +35944,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="1676" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1676" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1676" s="2" t="s">
         <v>5</v>
       </c>
@@ -36117,7 +36114,7 @@
         <v>1811</v>
       </c>
     </row>
-    <row r="1686" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1686" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1686" s="2" t="s">
         <v>5</v>
       </c>
@@ -36134,7 +36131,7 @@
         <v>1812</v>
       </c>
     </row>
-    <row r="1687" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1687" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1687" s="2" t="s">
         <v>5</v>
       </c>
@@ -36202,7 +36199,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1691" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1691" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1691" s="2" t="s">
         <v>5</v>
       </c>
@@ -36304,7 +36301,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="1697" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1697" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1697" s="2" t="s">
         <v>5</v>
       </c>
@@ -36389,7 +36386,7 @@
         <v>1827</v>
       </c>
     </row>
-    <row r="1702" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1702" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1702" s="2" t="s">
         <v>5</v>
       </c>
@@ -36440,7 +36437,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="1705" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1705" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1705" s="2" t="s">
         <v>5</v>
       </c>
@@ -36525,7 +36522,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="1710" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1710" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1710" s="2" t="s">
         <v>5</v>
       </c>
@@ -36576,7 +36573,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="1713" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1713" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1713" s="2" t="s">
         <v>5</v>
       </c>
@@ -36984,7 +36981,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="1737" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1737" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1737" s="2" t="s">
         <v>5</v>
       </c>
@@ -37052,7 +37049,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="1741" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1741" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1741" s="2" t="s">
         <v>5</v>
       </c>
@@ -37069,7 +37066,7 @@
         <v>1868</v>
       </c>
     </row>
-    <row r="1742" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1742" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1742" s="2" t="s">
         <v>5</v>
       </c>
@@ -37086,7 +37083,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="1743" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1743" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1743" s="2" t="s">
         <v>5</v>
       </c>
@@ -37171,7 +37168,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="1748" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1748" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1748" s="2" t="s">
         <v>5</v>
       </c>
@@ -37205,7 +37202,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="1750" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1750" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1750" s="2" t="s">
         <v>5</v>
       </c>
@@ -37222,7 +37219,7 @@
         <v>1879</v>
       </c>
     </row>
-    <row r="1751" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1751" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1751" s="2" t="s">
         <v>5</v>
       </c>
@@ -37256,7 +37253,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1753" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1753" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1753" s="2" t="s">
         <v>5</v>
       </c>
@@ -37426,7 +37423,7 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="1763" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1763" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1763" s="2" t="s">
         <v>5</v>
       </c>
@@ -37443,7 +37440,7 @@
         <v>1890</v>
       </c>
     </row>
-    <row r="1764" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1764" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1764" s="2" t="s">
         <v>5</v>
       </c>
@@ -37460,7 +37457,7 @@
         <v>1891</v>
       </c>
     </row>
-    <row r="1765" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1765" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1765" s="2" t="s">
         <v>5</v>
       </c>
@@ -37545,7 +37542,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="1770" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1770" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1770" s="2" t="s">
         <v>5</v>
       </c>
@@ -37919,7 +37916,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="1792" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1792" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1792" s="2" t="s">
         <v>5</v>
       </c>
@@ -37953,7 +37950,7 @@
         <v>1922</v>
       </c>
     </row>
-    <row r="1794" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1794" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1794" s="2" t="s">
         <v>5</v>
       </c>
@@ -38004,7 +38001,7 @@
         <v>1925</v>
       </c>
     </row>
-    <row r="1797" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1797" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1797" s="2" t="s">
         <v>5</v>
       </c>
@@ -38106,7 +38103,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="1803" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1803" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1803" s="2" t="s">
         <v>5</v>
       </c>
@@ -38259,7 +38256,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="1812" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1812" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1812" s="2" t="s">
         <v>5</v>
       </c>
@@ -38361,7 +38358,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="1818" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1818" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1818" s="2" t="s">
         <v>5</v>
       </c>
@@ -38548,7 +38545,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="1829" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1829" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1829" s="2" t="s">
         <v>5</v>
       </c>
@@ -38650,7 +38647,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="1835" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1835" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1835" s="2" t="s">
         <v>5</v>
       </c>
@@ -38684,7 +38681,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="1837" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1837" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1837" s="2" t="s">
         <v>5</v>
       </c>
@@ -38718,7 +38715,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="1839" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1839" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1839" s="2" t="s">
         <v>5</v>
       </c>
@@ -38752,7 +38749,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="1841" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1841" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1841" s="2" t="s">
         <v>5</v>
       </c>
@@ -38803,7 +38800,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="1844" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1844" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1844" s="2" t="s">
         <v>5</v>
       </c>
@@ -38956,7 +38953,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="1853" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1853" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1853" s="2" t="s">
         <v>5</v>
       </c>
@@ -39007,7 +39004,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="1856" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1856" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1856" s="2" t="s">
         <v>5</v>
       </c>
@@ -39024,7 +39021,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="1857" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1857" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1857" s="2" t="s">
         <v>5</v>
       </c>
@@ -39143,7 +39140,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="1864" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1864" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1864" s="2" t="s">
         <v>5</v>
       </c>
@@ -39160,7 +39157,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="1865" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1865" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1865" s="2" t="s">
         <v>5</v>
       </c>
@@ -39262,7 +39259,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="1871" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1871" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1871" s="2" t="s">
         <v>5</v>
       </c>
@@ -39296,7 +39293,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="1873" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1873" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1873" s="2" t="s">
         <v>5</v>
       </c>
@@ -39551,7 +39548,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="1888" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1888" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1888" s="2" t="s">
         <v>5</v>
       </c>
@@ -39619,7 +39616,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="1892" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1892" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1892" s="2" t="s">
         <v>5</v>
       </c>
@@ -39636,7 +39633,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="1893" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1893" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1893" s="2" t="s">
         <v>5</v>
       </c>
@@ -39670,7 +39667,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="1895" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1895" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1895" s="2" t="s">
         <v>5</v>
       </c>
@@ -39704,7 +39701,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="1897" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1897" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1897" s="2" t="s">
         <v>5</v>
       </c>
@@ -39738,7 +39735,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="1899" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1899" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1899" s="2" t="s">
         <v>5</v>
       </c>
@@ -39772,7 +39769,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="1901" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1901" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1901" s="2" t="s">
         <v>5</v>
       </c>
@@ -40095,7 +40092,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="1920" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1920" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1920" s="2" t="s">
         <v>5</v>
       </c>
@@ -40112,7 +40109,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="1921" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1921" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1921" s="2" t="s">
         <v>5</v>
       </c>
@@ -40129,7 +40126,7 @@
         <v>2052</v>
       </c>
     </row>
-    <row r="1922" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="1922" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1922" s="2" t="s">
         <v>5</v>
       </c>
@@ -40401,7 +40398,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="1938" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1938" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1938" s="2" t="s">
         <v>5</v>
       </c>
@@ -40707,7 +40704,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="1956" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1956" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1956" s="2" t="s">
         <v>5</v>
       </c>
@@ -40843,7 +40840,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="1964" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1964" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1964" s="2" t="s">
         <v>5</v>
       </c>
@@ -40860,7 +40857,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="1965" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1965" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1965" s="2" t="s">
         <v>5</v>
       </c>
@@ -41081,7 +41078,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="1978" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1978" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1978" s="2" t="s">
         <v>5</v>
       </c>
@@ -41353,7 +41350,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="1994" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1994" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1994" s="2" t="s">
         <v>5</v>
       </c>
@@ -41375,16 +41372,16 @@
         <v>5</v>
       </c>
       <c r="B1995" s="12" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C1995" s="12" t="s">
         <v>2117</v>
       </c>
-      <c r="C1995" s="12" t="s">
+      <c r="D1995" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="D1995" s="12" t="s">
+      <c r="E1995" s="3" t="s">
         <v>2119</v>
-      </c>
-      <c r="E1995" s="3" t="s">
-        <v>2120</v>
       </c>
     </row>
     <row r="1996" spans="1:5" x14ac:dyDescent="0.3">
@@ -41392,16 +41389,16 @@
         <v>5</v>
       </c>
       <c r="B1996" s="12" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C1996" s="12" t="s">
         <v>2117</v>
       </c>
-      <c r="C1996" s="12" t="s">
+      <c r="D1996" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="D1996" s="12" t="s">
-        <v>2119</v>
-      </c>
       <c r="E1996" s="3" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="1997" spans="1:5" x14ac:dyDescent="0.3">
@@ -41409,13 +41406,13 @@
         <v>5</v>
       </c>
       <c r="B1997" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C1997" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D1997" s="12" t="s">
         <v>2118</v>
-      </c>
-      <c r="D1997" s="12" t="s">
-        <v>2119</v>
       </c>
       <c r="E1997" s="3" t="s">
         <v>191</v>
@@ -41426,16 +41423,16 @@
         <v>5</v>
       </c>
       <c r="B1998" s="12" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C1998" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D1998" s="12" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E1998" s="3" t="s">
         <v>2122</v>
-      </c>
-      <c r="C1998" s="12" t="s">
-        <v>2118</v>
-      </c>
-      <c r="D1998" s="12" t="s">
-        <v>2119</v>
-      </c>
-      <c r="E1998" s="3" t="s">
-        <v>2123</v>
       </c>
     </row>
     <row r="1999" spans="1:5" x14ac:dyDescent="0.3">
@@ -41443,16 +41440,16 @@
         <v>5</v>
       </c>
       <c r="B1999" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C1999" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D1999" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="D1999" s="12" t="s">
-        <v>2119</v>
-      </c>
       <c r="E1999" s="3" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="2000" spans="1:5" x14ac:dyDescent="0.3">
@@ -41460,13 +41457,13 @@
         <v>5</v>
       </c>
       <c r="B2000" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2000" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2000" s="12" t="s">
         <v>2118</v>
-      </c>
-      <c r="D2000" s="12" t="s">
-        <v>2119</v>
       </c>
       <c r="E2000" s="3" t="s">
         <v>1561</v>
@@ -41477,33 +41474,33 @@
         <v>5</v>
       </c>
       <c r="B2001" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2001" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2001" s="12" t="s">
         <v>2118</v>
-      </c>
-      <c r="D2001" s="12" t="s">
-        <v>2119</v>
       </c>
       <c r="E2001" s="3" t="s">
         <v>1785</v>
       </c>
     </row>
-    <row r="2002" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2002" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2002" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B2002" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2002" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2002" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="D2002" s="12" t="s">
-        <v>2119</v>
-      </c>
       <c r="E2002" s="3" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="2003" spans="1:5" x14ac:dyDescent="0.3">
@@ -41511,33 +41508,33 @@
         <v>5</v>
       </c>
       <c r="B2003" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2003" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2003" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="D2003" s="12" t="s">
-        <v>2119</v>
-      </c>
       <c r="E2003" s="3" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2004" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2004" s="12" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C2004" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2004" s="12" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E2004" s="3" t="s">
         <v>2126</v>
-      </c>
-    </row>
-    <row r="2004" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2004" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2004" s="12" t="s">
-        <v>2122</v>
-      </c>
-      <c r="C2004" s="12" t="s">
-        <v>2118</v>
-      </c>
-      <c r="D2004" s="12" t="s">
-        <v>2119</v>
-      </c>
-      <c r="E2004" s="3" t="s">
-        <v>2127</v>
       </c>
     </row>
     <row r="2005" spans="1:5" x14ac:dyDescent="0.3">
@@ -41545,16 +41542,16 @@
         <v>5</v>
       </c>
       <c r="B2005" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2005" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2005" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="D2005" s="12" t="s">
-        <v>2119</v>
-      </c>
       <c r="E2005" s="3" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="2006" spans="1:5" x14ac:dyDescent="0.3">
@@ -41562,16 +41559,16 @@
         <v>5</v>
       </c>
       <c r="B2006" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2006" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2006" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="D2006" s="12" t="s">
-        <v>2119</v>
-      </c>
       <c r="E2006" s="3" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="2007" spans="1:5" x14ac:dyDescent="0.3">
@@ -41579,16 +41576,16 @@
         <v>5</v>
       </c>
       <c r="B2007" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2007" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2007" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="D2007" s="12" t="s">
-        <v>2119</v>
-      </c>
       <c r="E2007" s="3" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="2008" spans="1:5" x14ac:dyDescent="0.3">
@@ -41596,13 +41593,13 @@
         <v>5</v>
       </c>
       <c r="B2008" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2008" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2008" s="12" t="s">
         <v>2118</v>
-      </c>
-      <c r="D2008" s="12" t="s">
-        <v>2119</v>
       </c>
       <c r="E2008" s="3" t="s">
         <v>1589</v>
@@ -41613,16 +41610,16 @@
         <v>5</v>
       </c>
       <c r="B2009" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2009" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2009" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="D2009" s="12" t="s">
-        <v>2119</v>
-      </c>
       <c r="E2009" s="3" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="2010" spans="1:5" x14ac:dyDescent="0.3">
@@ -41630,16 +41627,16 @@
         <v>5</v>
       </c>
       <c r="B2010" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2010" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2010" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="D2010" s="12" t="s">
-        <v>2119</v>
-      </c>
       <c r="E2010" s="3" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="2011" spans="1:5" x14ac:dyDescent="0.3">
@@ -41647,16 +41644,16 @@
         <v>5</v>
       </c>
       <c r="B2011" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2011" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2011" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="D2011" s="12" t="s">
-        <v>2119</v>
-      </c>
       <c r="E2011" s="3" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="2012" spans="1:5" x14ac:dyDescent="0.3">
@@ -41664,13 +41661,13 @@
         <v>5</v>
       </c>
       <c r="B2012" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2012" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2012" s="12" t="s">
         <v>2118</v>
-      </c>
-      <c r="D2012" s="12" t="s">
-        <v>2119</v>
       </c>
       <c r="E2012" s="3" t="s">
         <v>1210</v>
@@ -41681,50 +41678,50 @@
         <v>5</v>
       </c>
       <c r="B2013" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2013" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2013" s="12" t="s">
         <v>2118</v>
-      </c>
-      <c r="D2013" s="12" t="s">
-        <v>2119</v>
       </c>
       <c r="E2013" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2014" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2014" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2014" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B2014" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2014" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2014" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="D2014" s="12" t="s">
-        <v>2119</v>
-      </c>
       <c r="E2014" s="3" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2015" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2015" s="12" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C2015" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2015" s="12" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E2015" s="3" t="s">
         <v>2134</v>
-      </c>
-    </row>
-    <row r="2015" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2015" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2015" s="12" t="s">
-        <v>2122</v>
-      </c>
-      <c r="C2015" s="12" t="s">
-        <v>2118</v>
-      </c>
-      <c r="D2015" s="12" t="s">
-        <v>2119</v>
-      </c>
-      <c r="E2015" s="3" t="s">
-        <v>2135</v>
       </c>
     </row>
     <row r="2016" spans="1:5" x14ac:dyDescent="0.3">
@@ -41732,16 +41729,16 @@
         <v>5</v>
       </c>
       <c r="B2016" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2016" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2016" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="D2016" s="12" t="s">
-        <v>2119</v>
-      </c>
       <c r="E2016" s="3" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="2017" spans="1:5" x14ac:dyDescent="0.3">
@@ -41749,16 +41746,16 @@
         <v>5</v>
       </c>
       <c r="B2017" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2017" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2017" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="D2017" s="12" t="s">
-        <v>2119</v>
-      </c>
       <c r="E2017" s="3" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="2018" spans="1:5" x14ac:dyDescent="0.3">
@@ -41766,16 +41763,16 @@
         <v>5</v>
       </c>
       <c r="B2018" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2018" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2018" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="D2018" s="12" t="s">
-        <v>2119</v>
-      </c>
       <c r="E2018" s="3" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="2019" spans="1:5" x14ac:dyDescent="0.3">
@@ -41783,13 +41780,13 @@
         <v>5</v>
       </c>
       <c r="B2019" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2019" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2019" s="12" t="s">
         <v>2118</v>
-      </c>
-      <c r="D2019" s="12" t="s">
-        <v>2119</v>
       </c>
       <c r="E2019" s="3" t="s">
         <v>2056</v>
@@ -41800,33 +41797,33 @@
         <v>5</v>
       </c>
       <c r="B2020" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2020" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2020" s="12" t="s">
         <v>2118</v>
-      </c>
-      <c r="D2020" s="12" t="s">
-        <v>2119</v>
       </c>
       <c r="E2020" s="3" t="s">
         <v>1631</v>
       </c>
     </row>
-    <row r="2021" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2021" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2021" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B2021" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2021" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2021" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="D2021" s="12" t="s">
-        <v>2119</v>
-      </c>
       <c r="E2021" s="3" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="2022" spans="1:5" x14ac:dyDescent="0.3">
@@ -41834,16 +41831,16 @@
         <v>5</v>
       </c>
       <c r="B2022" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2022" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2022" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="D2022" s="12" t="s">
-        <v>2119</v>
-      </c>
       <c r="E2022" s="3" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="2023" spans="1:5" x14ac:dyDescent="0.3">
@@ -41851,16 +41848,16 @@
         <v>5</v>
       </c>
       <c r="B2023" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2023" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2023" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="D2023" s="12" t="s">
-        <v>2119</v>
-      </c>
       <c r="E2023" s="3" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="2024" spans="1:5" x14ac:dyDescent="0.3">
@@ -41868,16 +41865,16 @@
         <v>5</v>
       </c>
       <c r="B2024" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2024" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2024" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="D2024" s="12" t="s">
-        <v>2119</v>
-      </c>
       <c r="E2024" s="3" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="2025" spans="1:5" x14ac:dyDescent="0.3">
@@ -41885,13 +41882,13 @@
         <v>5</v>
       </c>
       <c r="B2025" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2025" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2025" s="12" t="s">
         <v>2118</v>
-      </c>
-      <c r="D2025" s="12" t="s">
-        <v>2119</v>
       </c>
       <c r="E2025" s="3" t="s">
         <v>1343</v>
@@ -41902,16 +41899,16 @@
         <v>5</v>
       </c>
       <c r="B2026" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2026" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2026" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="D2026" s="12" t="s">
-        <v>2119</v>
-      </c>
       <c r="E2026" s="3" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="2027" spans="1:5" x14ac:dyDescent="0.3">
@@ -41919,16 +41916,16 @@
         <v>5</v>
       </c>
       <c r="B2027" s="12" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C2027" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2027" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="D2027" s="12" t="s">
-        <v>2119</v>
-      </c>
       <c r="E2027" s="3" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="2028" spans="1:5" x14ac:dyDescent="0.3">
@@ -41939,13 +41936,13 @@
         <v>295</v>
       </c>
       <c r="C2028" s="12" t="s">
+        <v>2144</v>
+      </c>
+      <c r="D2028" s="12" t="s">
         <v>2145</v>
       </c>
-      <c r="D2028" s="12" t="s">
+      <c r="E2028" s="3" t="s">
         <v>2146</v>
-      </c>
-      <c r="E2028" s="3" t="s">
-        <v>2147</v>
       </c>
     </row>
     <row r="2029" spans="1:5" x14ac:dyDescent="0.3">
@@ -41956,13 +41953,13 @@
         <v>295</v>
       </c>
       <c r="C2029" s="12" t="s">
+        <v>2144</v>
+      </c>
+      <c r="D2029" s="12" t="s">
         <v>2145</v>
       </c>
-      <c r="D2029" s="12" t="s">
-        <v>2146</v>
-      </c>
       <c r="E2029" s="3" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="2030" spans="1:5" x14ac:dyDescent="0.3">
@@ -41973,10 +41970,10 @@
         <v>295</v>
       </c>
       <c r="C2030" s="12" t="s">
+        <v>2144</v>
+      </c>
+      <c r="D2030" s="12" t="s">
         <v>2145</v>
-      </c>
-      <c r="D2030" s="12" t="s">
-        <v>2146</v>
       </c>
       <c r="E2030" s="3" t="s">
         <v>1581</v>
@@ -41990,13 +41987,13 @@
         <v>295</v>
       </c>
       <c r="C2031" s="12" t="s">
+        <v>2144</v>
+      </c>
+      <c r="D2031" s="12" t="s">
         <v>2145</v>
       </c>
-      <c r="D2031" s="12" t="s">
-        <v>2146</v>
-      </c>
       <c r="E2031" s="3" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="2032" spans="1:5" x14ac:dyDescent="0.3">
@@ -42007,16 +42004,16 @@
         <v>295</v>
       </c>
       <c r="C2032" s="12" t="s">
+        <v>2144</v>
+      </c>
+      <c r="D2032" s="12" t="s">
         <v>2145</v>
       </c>
-      <c r="D2032" s="12" t="s">
-        <v>2146</v>
-      </c>
       <c r="E2032" s="3" t="s">
-        <v>2150</v>
-      </c>
-    </row>
-    <row r="2033" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="2033" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2033" s="2" t="s">
         <v>5</v>
       </c>
@@ -42024,13 +42021,13 @@
         <v>295</v>
       </c>
       <c r="C2033" s="12" t="s">
+        <v>2144</v>
+      </c>
+      <c r="D2033" s="12" t="s">
         <v>2145</v>
       </c>
-      <c r="D2033" s="12" t="s">
-        <v>2146</v>
-      </c>
       <c r="E2033" s="3" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="2034" spans="1:5" x14ac:dyDescent="0.3">
@@ -42041,10 +42038,10 @@
         <v>295</v>
       </c>
       <c r="C2034" s="12" t="s">
+        <v>2144</v>
+      </c>
+      <c r="D2034" s="12" t="s">
         <v>2145</v>
-      </c>
-      <c r="D2034" s="12" t="s">
-        <v>2146</v>
       </c>
       <c r="E2034" s="3" t="s">
         <v>778</v>
@@ -42058,10 +42055,10 @@
         <v>295</v>
       </c>
       <c r="C2035" s="12" t="s">
+        <v>2144</v>
+      </c>
+      <c r="D2035" s="12" t="s">
         <v>2145</v>
-      </c>
-      <c r="D2035" s="12" t="s">
-        <v>2146</v>
       </c>
       <c r="E2035" s="3" t="s">
         <v>44</v>
@@ -42075,10 +42072,10 @@
         <v>295</v>
       </c>
       <c r="C2036" s="12" t="s">
+        <v>2144</v>
+      </c>
+      <c r="D2036" s="12" t="s">
         <v>2145</v>
-      </c>
-      <c r="D2036" s="12" t="s">
-        <v>2146</v>
       </c>
       <c r="E2036" s="3" t="s">
         <v>322</v>
@@ -42089,16 +42086,16 @@
         <v>5</v>
       </c>
       <c r="B2037" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2037" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2037" s="12" t="s">
+      <c r="D2037" s="12" t="s">
         <v>2153</v>
       </c>
-      <c r="D2037" s="12" t="s">
+      <c r="E2037" s="3" t="s">
         <v>2154</v>
-      </c>
-      <c r="E2037" s="3" t="s">
-        <v>2155</v>
       </c>
     </row>
     <row r="2038" spans="1:5" x14ac:dyDescent="0.3">
@@ -42106,16 +42103,16 @@
         <v>5</v>
       </c>
       <c r="B2038" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2038" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2038" s="12" t="s">
+      <c r="D2038" s="12" t="s">
         <v>2153</v>
       </c>
-      <c r="D2038" s="12" t="s">
-        <v>2154</v>
-      </c>
       <c r="E2038" s="3" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="2039" spans="1:5" x14ac:dyDescent="0.3">
@@ -42123,16 +42120,16 @@
         <v>5</v>
       </c>
       <c r="B2039" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2039" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2039" s="12" t="s">
+      <c r="D2039" s="12" t="s">
         <v>2153</v>
       </c>
-      <c r="D2039" s="12" t="s">
-        <v>2154</v>
-      </c>
       <c r="E2039" s="3" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="2040" spans="1:5" x14ac:dyDescent="0.3">
@@ -42140,16 +42137,16 @@
         <v>5</v>
       </c>
       <c r="B2040" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2040" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2040" s="12" t="s">
+      <c r="D2040" s="12" t="s">
         <v>2153</v>
       </c>
-      <c r="D2040" s="12" t="s">
-        <v>2154</v>
-      </c>
       <c r="E2040" s="3" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="2041" spans="1:5" x14ac:dyDescent="0.3">
@@ -42157,33 +42154,33 @@
         <v>5</v>
       </c>
       <c r="B2041" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2041" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2041" s="12" t="s">
+      <c r="D2041" s="12" t="s">
         <v>2153</v>
       </c>
-      <c r="D2041" s="12" t="s">
-        <v>2154</v>
-      </c>
       <c r="E2041" s="3" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="2042" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2042" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2042" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2042" s="12" t="s">
+        <v>2152</v>
+      </c>
+      <c r="D2042" s="12" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E2042" s="3" t="s">
         <v>2159</v>
-      </c>
-    </row>
-    <row r="2042" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2042" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2042" s="12" t="s">
-        <v>2152</v>
-      </c>
-      <c r="C2042" s="12" t="s">
-        <v>2153</v>
-      </c>
-      <c r="D2042" s="12" t="s">
-        <v>2154</v>
-      </c>
-      <c r="E2042" s="3" t="s">
-        <v>2160</v>
       </c>
     </row>
     <row r="2043" spans="1:5" x14ac:dyDescent="0.3">
@@ -42191,16 +42188,16 @@
         <v>5</v>
       </c>
       <c r="B2043" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2043" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2043" s="12" t="s">
+      <c r="D2043" s="12" t="s">
         <v>2153</v>
       </c>
-      <c r="D2043" s="12" t="s">
-        <v>2154</v>
-      </c>
       <c r="E2043" s="3" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="2044" spans="1:5" x14ac:dyDescent="0.3">
@@ -42208,16 +42205,16 @@
         <v>5</v>
       </c>
       <c r="B2044" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2044" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2044" s="12" t="s">
+      <c r="D2044" s="12" t="s">
         <v>2153</v>
       </c>
-      <c r="D2044" s="12" t="s">
-        <v>2154</v>
-      </c>
       <c r="E2044" s="3" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="2045" spans="1:5" x14ac:dyDescent="0.3">
@@ -42225,16 +42222,16 @@
         <v>5</v>
       </c>
       <c r="B2045" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2045" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2045" s="12" t="s">
+      <c r="D2045" s="12" t="s">
         <v>2153</v>
       </c>
-      <c r="D2045" s="12" t="s">
-        <v>2154</v>
-      </c>
       <c r="E2045" s="3" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="2046" spans="1:5" x14ac:dyDescent="0.3">
@@ -42242,16 +42239,16 @@
         <v>5</v>
       </c>
       <c r="B2046" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2046" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2046" s="12" t="s">
-        <v>2153</v>
-      </c>
       <c r="D2046" s="12" t="s">
+        <v>2163</v>
+      </c>
+      <c r="E2046" s="3" t="s">
         <v>2164</v>
-      </c>
-      <c r="E2046" s="3" t="s">
-        <v>2165</v>
       </c>
     </row>
     <row r="2047" spans="1:5" x14ac:dyDescent="0.3">
@@ -42259,16 +42256,16 @@
         <v>5</v>
       </c>
       <c r="B2047" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2047" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2047" s="12" t="s">
-        <v>2153</v>
-      </c>
       <c r="D2047" s="12" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="E2047" s="3" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="2048" spans="1:5" x14ac:dyDescent="0.3">
@@ -42276,16 +42273,16 @@
         <v>5</v>
       </c>
       <c r="B2048" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2048" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2048" s="12" t="s">
-        <v>2153</v>
-      </c>
       <c r="D2048" s="12" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="E2048" s="3" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="2049" spans="1:5" x14ac:dyDescent="0.3">
@@ -42293,16 +42290,16 @@
         <v>5</v>
       </c>
       <c r="B2049" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2049" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2049" s="12" t="s">
-        <v>2153</v>
-      </c>
       <c r="D2049" s="12" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="E2049" s="3" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="2050" spans="1:5" x14ac:dyDescent="0.3">
@@ -42310,16 +42307,16 @@
         <v>5</v>
       </c>
       <c r="B2050" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2050" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2050" s="12" t="s">
-        <v>2153</v>
-      </c>
       <c r="D2050" s="12" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="E2050" s="3" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="2051" spans="1:5" x14ac:dyDescent="0.3">
@@ -42327,16 +42324,16 @@
         <v>5</v>
       </c>
       <c r="B2051" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2051" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2051" s="12" t="s">
-        <v>2153</v>
-      </c>
       <c r="D2051" s="12" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="E2051" s="3" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="2052" spans="1:5" x14ac:dyDescent="0.3">
@@ -42344,16 +42341,16 @@
         <v>5</v>
       </c>
       <c r="B2052" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2052" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2052" s="12" t="s">
-        <v>2153</v>
-      </c>
       <c r="D2052" s="12" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="E2052" s="3" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="2053" spans="1:5" x14ac:dyDescent="0.3">
@@ -42361,16 +42358,16 @@
         <v>5</v>
       </c>
       <c r="B2053" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2053" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2053" s="12" t="s">
-        <v>2153</v>
-      </c>
       <c r="D2053" s="12" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="E2053" s="3" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="2054" spans="1:5" x14ac:dyDescent="0.3">
@@ -42378,16 +42375,16 @@
         <v>5</v>
       </c>
       <c r="B2054" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2054" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2054" s="12" t="s">
-        <v>2153</v>
-      </c>
       <c r="D2054" s="12" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="E2054" s="3" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="2055" spans="1:5" x14ac:dyDescent="0.3">
@@ -42395,16 +42392,16 @@
         <v>5</v>
       </c>
       <c r="B2055" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2055" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2055" s="12" t="s">
-        <v>2153</v>
-      </c>
       <c r="D2055" s="12" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="E2055" s="3" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="2056" spans="1:5" x14ac:dyDescent="0.3">
@@ -42412,16 +42409,16 @@
         <v>5</v>
       </c>
       <c r="B2056" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2056" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2056" s="12" t="s">
-        <v>2153</v>
-      </c>
       <c r="D2056" s="12" t="s">
+        <v>2174</v>
+      </c>
+      <c r="E2056" s="3" t="s">
         <v>2175</v>
-      </c>
-      <c r="E2056" s="3" t="s">
-        <v>2176</v>
       </c>
     </row>
     <row r="2057" spans="1:5" x14ac:dyDescent="0.3">
@@ -42429,16 +42426,16 @@
         <v>5</v>
       </c>
       <c r="B2057" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2057" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2057" s="12" t="s">
-        <v>2153</v>
-      </c>
       <c r="D2057" s="12" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="E2057" s="3" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="2058" spans="1:5" x14ac:dyDescent="0.3">
@@ -42446,33 +42443,33 @@
         <v>5</v>
       </c>
       <c r="B2058" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2058" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2058" s="12" t="s">
-        <v>2153</v>
-      </c>
       <c r="D2058" s="12" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="E2058" s="3" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2059" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2059" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2059" s="12" t="s">
+        <v>2152</v>
+      </c>
+      <c r="D2059" s="12" t="s">
+        <v>2174</v>
+      </c>
+      <c r="E2059" s="3" t="s">
         <v>2178</v>
-      </c>
-    </row>
-    <row r="2059" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2059" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2059" s="12" t="s">
-        <v>2152</v>
-      </c>
-      <c r="C2059" s="12" t="s">
-        <v>2153</v>
-      </c>
-      <c r="D2059" s="12" t="s">
-        <v>2175</v>
-      </c>
-      <c r="E2059" s="3" t="s">
-        <v>2179</v>
       </c>
     </row>
     <row r="2060" spans="1:5" x14ac:dyDescent="0.3">
@@ -42480,13 +42477,13 @@
         <v>5</v>
       </c>
       <c r="B2060" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2060" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2060" s="12" t="s">
-        <v>2153</v>
-      </c>
       <c r="D2060" s="12" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="E2060" s="3" t="s">
         <v>791</v>
@@ -42497,16 +42494,16 @@
         <v>5</v>
       </c>
       <c r="B2061" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2061" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2061" s="12" t="s">
-        <v>2153</v>
-      </c>
       <c r="D2061" s="12" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="E2061" s="3" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="2062" spans="1:5" x14ac:dyDescent="0.3">
@@ -42514,16 +42511,16 @@
         <v>5</v>
       </c>
       <c r="B2062" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2062" s="12" t="s">
         <v>2152</v>
       </c>
-      <c r="C2062" s="12" t="s">
-        <v>2153</v>
-      </c>
       <c r="D2062" s="12" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="E2062" s="3" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="2063" spans="1:5" x14ac:dyDescent="0.3">
@@ -42531,10 +42528,10 @@
         <v>5</v>
       </c>
       <c r="B2063" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2063" s="12" t="s">
         <v>2152</v>
-      </c>
-      <c r="C2063" s="12" t="s">
-        <v>2153</v>
       </c>
       <c r="D2063" s="12" t="s">
         <v>2020</v>
@@ -42548,16 +42545,16 @@
         <v>5</v>
       </c>
       <c r="B2064" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2064" s="12" t="s">
         <v>2152</v>
-      </c>
-      <c r="C2064" s="12" t="s">
-        <v>2153</v>
       </c>
       <c r="D2064" s="12" t="s">
         <v>2020</v>
       </c>
       <c r="E2064" s="3" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="2065" spans="1:5" x14ac:dyDescent="0.3">
@@ -42565,16 +42562,16 @@
         <v>5</v>
       </c>
       <c r="B2065" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2065" s="12" t="s">
         <v>2152</v>
-      </c>
-      <c r="C2065" s="12" t="s">
-        <v>2153</v>
       </c>
       <c r="D2065" s="12" t="s">
         <v>2020</v>
       </c>
       <c r="E2065" s="3" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="2066" spans="1:5" x14ac:dyDescent="0.3">
@@ -42582,16 +42579,16 @@
         <v>5</v>
       </c>
       <c r="B2066" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2066" s="12" t="s">
         <v>2152</v>
-      </c>
-      <c r="C2066" s="12" t="s">
-        <v>2153</v>
       </c>
       <c r="D2066" s="12" t="s">
         <v>2020</v>
       </c>
       <c r="E2066" s="3" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="2067" spans="1:5" x14ac:dyDescent="0.3">
@@ -42599,16 +42596,16 @@
         <v>5</v>
       </c>
       <c r="B2067" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2067" s="12" t="s">
         <v>2152</v>
-      </c>
-      <c r="C2067" s="12" t="s">
-        <v>2153</v>
       </c>
       <c r="D2067" s="12" t="s">
         <v>2020</v>
       </c>
       <c r="E2067" s="3" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="2068" spans="1:5" x14ac:dyDescent="0.3">
@@ -42616,16 +42613,16 @@
         <v>5</v>
       </c>
       <c r="B2068" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2068" s="12" t="s">
         <v>2152</v>
-      </c>
-      <c r="C2068" s="12" t="s">
-        <v>2153</v>
       </c>
       <c r="D2068" s="12" t="s">
         <v>2020</v>
       </c>
       <c r="E2068" s="3" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="2069" spans="1:5" x14ac:dyDescent="0.3">
@@ -42633,16 +42630,16 @@
         <v>5</v>
       </c>
       <c r="B2069" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2069" s="12" t="s">
         <v>2152</v>
-      </c>
-      <c r="C2069" s="12" t="s">
-        <v>2153</v>
       </c>
       <c r="D2069" s="12" t="s">
         <v>2020</v>
       </c>
       <c r="E2069" s="3" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="2070" spans="1:5" x14ac:dyDescent="0.3">
@@ -42650,16 +42647,16 @@
         <v>5</v>
       </c>
       <c r="B2070" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2070" s="12" t="s">
         <v>2152</v>
-      </c>
-      <c r="C2070" s="12" t="s">
-        <v>2153</v>
       </c>
       <c r="D2070" s="12" t="s">
         <v>2020</v>
       </c>
       <c r="E2070" s="3" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="2071" spans="1:5" x14ac:dyDescent="0.3">
@@ -42667,16 +42664,16 @@
         <v>5</v>
       </c>
       <c r="B2071" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2071" s="12" t="s">
         <v>2152</v>
-      </c>
-      <c r="C2071" s="12" t="s">
-        <v>2153</v>
       </c>
       <c r="D2071" s="12" t="s">
         <v>2020</v>
       </c>
       <c r="E2071" s="3" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="2072" spans="1:5" x14ac:dyDescent="0.3">
@@ -42687,13 +42684,13 @@
         <v>48</v>
       </c>
       <c r="C2072" s="12" t="s">
+        <v>2189</v>
+      </c>
+      <c r="D2072" s="12" t="s">
         <v>2190</v>
       </c>
-      <c r="D2072" s="12" t="s">
+      <c r="E2072" s="3" t="s">
         <v>2191</v>
-      </c>
-      <c r="E2072" s="3" t="s">
-        <v>2192</v>
       </c>
     </row>
     <row r="2073" spans="1:5" x14ac:dyDescent="0.3">
@@ -42704,16 +42701,16 @@
         <v>48</v>
       </c>
       <c r="C2073" s="12" t="s">
+        <v>2189</v>
+      </c>
+      <c r="D2073" s="12" t="s">
         <v>2190</v>
       </c>
-      <c r="D2073" s="12" t="s">
-        <v>2191</v>
-      </c>
       <c r="E2073" s="3" t="s">
-        <v>2193</v>
-      </c>
-    </row>
-    <row r="2074" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>2192</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2074" s="2" t="s">
         <v>5</v>
       </c>
@@ -42721,13 +42718,13 @@
         <v>48</v>
       </c>
       <c r="C2074" s="12" t="s">
+        <v>2189</v>
+      </c>
+      <c r="D2074" s="12" t="s">
         <v>2190</v>
       </c>
-      <c r="D2074" s="12" t="s">
-        <v>2191</v>
-      </c>
       <c r="E2074" s="3" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="2075" spans="1:5" x14ac:dyDescent="0.3">
@@ -42738,13 +42735,13 @@
         <v>48</v>
       </c>
       <c r="C2075" s="12" t="s">
+        <v>2189</v>
+      </c>
+      <c r="D2075" s="12" t="s">
         <v>2190</v>
       </c>
-      <c r="D2075" s="12" t="s">
-        <v>2191</v>
-      </c>
       <c r="E2075" s="3" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="2076" spans="1:5" x14ac:dyDescent="0.3">
@@ -42755,13 +42752,13 @@
         <v>48</v>
       </c>
       <c r="C2076" s="12" t="s">
+        <v>2189</v>
+      </c>
+      <c r="D2076" s="12" t="s">
         <v>2190</v>
       </c>
-      <c r="D2076" s="12" t="s">
-        <v>2191</v>
-      </c>
       <c r="E2076" s="3" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="2077" spans="1:5" x14ac:dyDescent="0.3">
@@ -42772,13 +42769,13 @@
         <v>48</v>
       </c>
       <c r="C2077" s="12" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D2077" s="12" t="s">
+        <v>2196</v>
+      </c>
+      <c r="E2077" s="3" t="s">
         <v>2197</v>
-      </c>
-      <c r="E2077" s="3" t="s">
-        <v>2198</v>
       </c>
     </row>
     <row r="2078" spans="1:5" x14ac:dyDescent="0.3">
@@ -42789,13 +42786,13 @@
         <v>48</v>
       </c>
       <c r="C2078" s="12" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D2078" s="12" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="E2078" s="3" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="2079" spans="1:5" x14ac:dyDescent="0.3">
@@ -42806,10 +42803,10 @@
         <v>48</v>
       </c>
       <c r="C2079" s="12" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D2079" s="12" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="E2079" s="3" t="s">
         <v>2099</v>
@@ -42823,13 +42820,13 @@
         <v>48</v>
       </c>
       <c r="C2080" s="12" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D2080" s="12" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="E2080" s="3" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="2081" spans="1:5" x14ac:dyDescent="0.3">
@@ -42840,10 +42837,10 @@
         <v>48</v>
       </c>
       <c r="C2081" s="12" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D2081" s="12" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="E2081" s="3" t="s">
         <v>1632</v>
@@ -42857,13 +42854,13 @@
         <v>48</v>
       </c>
       <c r="C2082" s="4" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D2082" s="4" t="s">
+        <v>2200</v>
+      </c>
+      <c r="E2082" s="5" t="s">
         <v>2201</v>
-      </c>
-      <c r="E2082" s="5" t="s">
-        <v>2202</v>
       </c>
     </row>
     <row r="2083" spans="1:5" x14ac:dyDescent="0.3">
@@ -42874,16 +42871,16 @@
         <v>48</v>
       </c>
       <c r="C2083" s="4" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D2083" s="4" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="E2083" s="5" t="s">
-        <v>2203</v>
-      </c>
-    </row>
-    <row r="2084" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2084" s="2" t="s">
         <v>5</v>
       </c>
@@ -42891,16 +42888,16 @@
         <v>48</v>
       </c>
       <c r="C2084" s="4" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D2084" s="4" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="E2084" s="5" t="s">
-        <v>2204</v>
-      </c>
-    </row>
-    <row r="2085" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>2203</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2085" s="2" t="s">
         <v>5</v>
       </c>
@@ -42908,13 +42905,13 @@
         <v>48</v>
       </c>
       <c r="C2085" s="4" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D2085" s="4" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="E2085" s="5" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="2086" spans="1:5" x14ac:dyDescent="0.3">
@@ -42925,13 +42922,13 @@
         <v>48</v>
       </c>
       <c r="C2086" s="4" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D2086" s="4" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="E2086" s="5" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="2087" spans="1:5" x14ac:dyDescent="0.3">
@@ -42942,10 +42939,10 @@
         <v>48</v>
       </c>
       <c r="C2087" s="12" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D2087" s="12" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="E2087" s="3" t="s">
         <v>1841</v>
@@ -42959,10 +42956,10 @@
         <v>48</v>
       </c>
       <c r="C2088" s="12" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D2088" s="12" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="E2088" s="3" t="s">
         <v>252</v>
@@ -42976,13 +42973,13 @@
         <v>48</v>
       </c>
       <c r="C2089" s="12" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D2089" s="12" t="s">
+        <v>2206</v>
+      </c>
+      <c r="E2089" s="3" t="s">
         <v>2207</v>
-      </c>
-      <c r="E2089" s="3" t="s">
-        <v>2208</v>
       </c>
     </row>
     <row r="2090" spans="1:5" x14ac:dyDescent="0.3">
@@ -42993,10 +42990,10 @@
         <v>48</v>
       </c>
       <c r="C2090" s="12" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D2090" s="12" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="E2090" s="3" t="s">
         <v>222</v>
@@ -43010,13 +43007,13 @@
         <v>48</v>
       </c>
       <c r="C2091" s="12" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D2091" s="12" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="E2091" s="3" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="2092" spans="1:5" x14ac:dyDescent="0.3">
@@ -43027,13 +43024,13 @@
         <v>48</v>
       </c>
       <c r="C2092" s="4" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D2092" s="4" t="s">
+        <v>2209</v>
+      </c>
+      <c r="E2092" s="5" t="s">
         <v>2210</v>
-      </c>
-      <c r="E2092" s="5" t="s">
-        <v>2211</v>
       </c>
     </row>
     <row r="2093" spans="1:5" x14ac:dyDescent="0.3">
@@ -43044,13 +43041,13 @@
         <v>48</v>
       </c>
       <c r="C2093" s="4" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D2093" s="4" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="E2093" s="5" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="2094" spans="1:5" x14ac:dyDescent="0.3">
@@ -43061,13 +43058,13 @@
         <v>48</v>
       </c>
       <c r="C2094" s="4" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D2094" s="4" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="E2094" s="5" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="2095" spans="1:5" x14ac:dyDescent="0.3">
@@ -43078,13 +43075,13 @@
         <v>48</v>
       </c>
       <c r="C2095" s="4" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D2095" s="4" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="E2095" s="5" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="2096" spans="1:5" x14ac:dyDescent="0.3">
@@ -43095,7 +43092,7 @@
         <v>1399</v>
       </c>
       <c r="C2096" s="12" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="D2096" s="12" t="s">
         <v>1399</v>
@@ -43112,7 +43109,7 @@
         <v>1399</v>
       </c>
       <c r="C2097" s="12" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="D2097" s="12" t="s">
         <v>1399</v>
@@ -43129,13 +43126,13 @@
         <v>1399</v>
       </c>
       <c r="C2098" s="12" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="D2098" s="12" t="s">
         <v>1399</v>
       </c>
       <c r="E2098" s="3" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="2099" spans="1:5" x14ac:dyDescent="0.3">
@@ -43146,16 +43143,16 @@
         <v>1399</v>
       </c>
       <c r="C2099" s="12" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="D2099" s="12" t="s">
         <v>1399</v>
       </c>
       <c r="E2099" s="3" t="s">
-        <v>2216</v>
-      </c>
-    </row>
-    <row r="2100" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2100" s="2" t="s">
         <v>5</v>
       </c>
@@ -43163,13 +43160,13 @@
         <v>1399</v>
       </c>
       <c r="C2100" s="12" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="D2100" s="12" t="s">
         <v>1399</v>
       </c>
       <c r="E2100" s="3" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="2101" spans="1:5" x14ac:dyDescent="0.3">
@@ -43180,7 +43177,7 @@
         <v>1399</v>
       </c>
       <c r="C2101" s="12" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="D2101" s="12" t="s">
         <v>1399</v>
@@ -43197,13 +43194,13 @@
         <v>1399</v>
       </c>
       <c r="C2102" s="12" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="D2102" s="12" t="s">
         <v>1399</v>
       </c>
       <c r="E2102" s="3" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="2103" spans="1:5" x14ac:dyDescent="0.3">
@@ -43214,13 +43211,13 @@
         <v>1399</v>
       </c>
       <c r="C2103" s="12" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="D2103" s="12" t="s">
         <v>1399</v>
       </c>
       <c r="E2103" s="3" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="2104" spans="1:5" x14ac:dyDescent="0.3">
@@ -43228,13 +43225,13 @@
         <v>5</v>
       </c>
       <c r="B2104" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2104" s="4" t="s">
         <v>2220</v>
       </c>
-      <c r="C2104" s="4" t="s">
+      <c r="D2104" s="4" t="s">
         <v>2221</v>
-      </c>
-      <c r="D2104" s="4" t="s">
-        <v>2222</v>
       </c>
       <c r="E2104" s="5" t="s">
         <v>191</v>
@@ -43245,16 +43242,16 @@
         <v>5</v>
       </c>
       <c r="B2105" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2105" s="4" t="s">
         <v>2220</v>
       </c>
-      <c r="C2105" s="4" t="s">
+      <c r="D2105" s="4" t="s">
         <v>2221</v>
       </c>
-      <c r="D2105" s="4" t="s">
+      <c r="E2105" s="5" t="s">
         <v>2222</v>
-      </c>
-      <c r="E2105" s="5" t="s">
-        <v>2223</v>
       </c>
     </row>
     <row r="2106" spans="1:5" x14ac:dyDescent="0.3">
@@ -43262,13 +43259,13 @@
         <v>5</v>
       </c>
       <c r="B2106" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2106" s="4" t="s">
         <v>2220</v>
       </c>
-      <c r="C2106" s="4" t="s">
+      <c r="D2106" s="4" t="s">
         <v>2221</v>
-      </c>
-      <c r="D2106" s="4" t="s">
-        <v>2222</v>
       </c>
       <c r="E2106" s="5" t="s">
         <v>1925</v>
@@ -43279,33 +43276,33 @@
         <v>5</v>
       </c>
       <c r="B2107" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2107" s="4" t="s">
         <v>2220</v>
       </c>
-      <c r="C2107" s="4" t="s">
+      <c r="D2107" s="4" t="s">
         <v>2221</v>
       </c>
-      <c r="D2107" s="4" t="s">
-        <v>2222</v>
-      </c>
       <c r="E2107" s="5" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2108" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2108" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2108" s="4" t="s">
+        <v>2220</v>
+      </c>
+      <c r="D2108" s="4" t="s">
+        <v>2221</v>
+      </c>
+      <c r="E2108" s="5" t="s">
         <v>2224</v>
-      </c>
-    </row>
-    <row r="2108" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2108" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2108" s="4" t="s">
-        <v>2220</v>
-      </c>
-      <c r="C2108" s="4" t="s">
-        <v>2221</v>
-      </c>
-      <c r="D2108" s="4" t="s">
-        <v>2222</v>
-      </c>
-      <c r="E2108" s="5" t="s">
-        <v>2225</v>
       </c>
     </row>
     <row r="2109" spans="1:5" x14ac:dyDescent="0.3">
@@ -43313,16 +43310,16 @@
         <v>5</v>
       </c>
       <c r="B2109" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2109" s="4" t="s">
         <v>2220</v>
       </c>
-      <c r="C2109" s="4" t="s">
+      <c r="D2109" s="4" t="s">
         <v>2221</v>
       </c>
-      <c r="D2109" s="4" t="s">
-        <v>2222</v>
-      </c>
       <c r="E2109" s="5" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="2110" spans="1:5" x14ac:dyDescent="0.3">
@@ -43330,16 +43327,16 @@
         <v>5</v>
       </c>
       <c r="B2110" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2110" s="4" t="s">
         <v>2220</v>
       </c>
-      <c r="C2110" s="4" t="s">
+      <c r="D2110" s="4" t="s">
         <v>2221</v>
       </c>
-      <c r="D2110" s="4" t="s">
-        <v>2222</v>
-      </c>
       <c r="E2110" s="5" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="2111" spans="1:5" x14ac:dyDescent="0.3">
@@ -43347,16 +43344,16 @@
         <v>5</v>
       </c>
       <c r="B2111" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2111" s="4" t="s">
         <v>2220</v>
       </c>
-      <c r="C2111" s="4" t="s">
+      <c r="D2111" s="4" t="s">
         <v>2221</v>
       </c>
-      <c r="D2111" s="4" t="s">
-        <v>2222</v>
-      </c>
       <c r="E2111" s="5" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="2112" spans="1:5" x14ac:dyDescent="0.3">
@@ -43364,16 +43361,16 @@
         <v>5</v>
       </c>
       <c r="B2112" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2112" s="4" t="s">
         <v>2220</v>
       </c>
-      <c r="C2112" s="4" t="s">
+      <c r="D2112" s="4" t="s">
         <v>2221</v>
       </c>
-      <c r="D2112" s="4" t="s">
-        <v>2222</v>
-      </c>
       <c r="E2112" s="5" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="2113" spans="1:5" x14ac:dyDescent="0.3">
@@ -43381,16 +43378,16 @@
         <v>5</v>
       </c>
       <c r="B2113" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2113" s="4" t="s">
         <v>2220</v>
       </c>
-      <c r="C2113" s="4" t="s">
+      <c r="D2113" s="4" t="s">
         <v>2221</v>
       </c>
-      <c r="D2113" s="4" t="s">
-        <v>2222</v>
-      </c>
       <c r="E2113" s="5" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="2114" spans="1:5" x14ac:dyDescent="0.3">
@@ -43398,16 +43395,16 @@
         <v>5</v>
       </c>
       <c r="B2114" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2114" s="4" t="s">
         <v>2220</v>
       </c>
-      <c r="C2114" s="4" t="s">
+      <c r="D2114" s="4" t="s">
         <v>2221</v>
       </c>
-      <c r="D2114" s="4" t="s">
-        <v>2222</v>
-      </c>
       <c r="E2114" s="5" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="2115" spans="1:5" x14ac:dyDescent="0.3">
@@ -43415,16 +43412,16 @@
         <v>5</v>
       </c>
       <c r="B2115" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2115" s="4" t="s">
         <v>2220</v>
       </c>
-      <c r="C2115" s="4" t="s">
+      <c r="D2115" s="4" t="s">
         <v>2221</v>
       </c>
-      <c r="D2115" s="4" t="s">
-        <v>2222</v>
-      </c>
       <c r="E2115" s="5" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="2116" spans="1:5" x14ac:dyDescent="0.3">
@@ -43432,16 +43429,16 @@
         <v>5</v>
       </c>
       <c r="B2116" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2116" s="4" t="s">
         <v>2220</v>
       </c>
-      <c r="C2116" s="4" t="s">
+      <c r="D2116" s="4" t="s">
         <v>2221</v>
       </c>
-      <c r="D2116" s="4" t="s">
-        <v>2222</v>
-      </c>
       <c r="E2116" s="5" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="2117" spans="1:5" x14ac:dyDescent="0.3">
@@ -43449,16 +43446,16 @@
         <v>5</v>
       </c>
       <c r="B2117" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2117" s="4" t="s">
         <v>2220</v>
       </c>
-      <c r="C2117" s="4" t="s">
+      <c r="D2117" s="4" t="s">
         <v>2221</v>
       </c>
-      <c r="D2117" s="4" t="s">
-        <v>2222</v>
-      </c>
       <c r="E2117" s="5" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="2118" spans="1:5" x14ac:dyDescent="0.3">
@@ -43466,13 +43463,13 @@
         <v>5</v>
       </c>
       <c r="B2118" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2118" s="4" t="s">
         <v>2220</v>
       </c>
-      <c r="C2118" s="4" t="s">
+      <c r="D2118" s="4" t="s">
         <v>2221</v>
-      </c>
-      <c r="D2118" s="4" t="s">
-        <v>2222</v>
       </c>
       <c r="E2118" s="5" t="s">
         <v>457</v>
@@ -43483,33 +43480,33 @@
         <v>5</v>
       </c>
       <c r="B2119" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2119" s="4" t="s">
         <v>2220</v>
       </c>
-      <c r="C2119" s="4" t="s">
+      <c r="D2119" s="4" t="s">
         <v>2221</v>
       </c>
-      <c r="D2119" s="4" t="s">
-        <v>2222</v>
-      </c>
       <c r="E2119" s="5" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2120" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2120" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2120" s="4" t="s">
+        <v>2220</v>
+      </c>
+      <c r="D2120" s="4" t="s">
+        <v>2221</v>
+      </c>
+      <c r="E2120" s="5" t="s">
         <v>2235</v>
-      </c>
-    </row>
-    <row r="2120" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2120" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2120" s="4" t="s">
-        <v>2220</v>
-      </c>
-      <c r="C2120" s="4" t="s">
-        <v>2221</v>
-      </c>
-      <c r="D2120" s="4" t="s">
-        <v>2222</v>
-      </c>
-      <c r="E2120" s="5" t="s">
-        <v>2236</v>
       </c>
     </row>
     <row r="2121" spans="1:5" x14ac:dyDescent="0.3">
@@ -43517,16 +43514,16 @@
         <v>5</v>
       </c>
       <c r="B2121" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2121" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D2121" s="4" t="s">
         <v>2237</v>
       </c>
-      <c r="D2121" s="4" t="s">
+      <c r="E2121" s="5" t="s">
         <v>2238</v>
-      </c>
-      <c r="E2121" s="5" t="s">
-        <v>2239</v>
       </c>
     </row>
     <row r="2122" spans="1:5" x14ac:dyDescent="0.3">
@@ -43534,16 +43531,16 @@
         <v>5</v>
       </c>
       <c r="B2122" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2122" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D2122" s="4" t="s">
         <v>2237</v>
       </c>
-      <c r="D2122" s="4" t="s">
-        <v>2238</v>
-      </c>
       <c r="E2122" s="5" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="2123" spans="1:5" x14ac:dyDescent="0.3">
@@ -43551,16 +43548,16 @@
         <v>5</v>
       </c>
       <c r="B2123" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2123" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D2123" s="4" t="s">
         <v>2237</v>
       </c>
-      <c r="D2123" s="4" t="s">
-        <v>2238</v>
-      </c>
       <c r="E2123" s="5" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="2124" spans="1:5" x14ac:dyDescent="0.3">
@@ -43568,13 +43565,13 @@
         <v>5</v>
       </c>
       <c r="B2124" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2124" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D2124" s="4" t="s">
         <v>2237</v>
-      </c>
-      <c r="D2124" s="4" t="s">
-        <v>2238</v>
       </c>
       <c r="E2124" s="5" t="s">
         <v>10</v>
@@ -43585,16 +43582,16 @@
         <v>5</v>
       </c>
       <c r="B2125" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2125" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D2125" s="4" t="s">
         <v>2237</v>
       </c>
-      <c r="D2125" s="4" t="s">
-        <v>2238</v>
-      </c>
       <c r="E2125" s="5" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="2126" spans="1:5" x14ac:dyDescent="0.3">
@@ -43602,16 +43599,16 @@
         <v>5</v>
       </c>
       <c r="B2126" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2126" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D2126" s="4" t="s">
         <v>2237</v>
       </c>
-      <c r="D2126" s="4" t="s">
-        <v>2238</v>
-      </c>
       <c r="E2126" s="5" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="2127" spans="1:5" x14ac:dyDescent="0.3">
@@ -43619,13 +43616,13 @@
         <v>5</v>
       </c>
       <c r="B2127" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2127" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D2127" s="4" t="s">
         <v>2237</v>
-      </c>
-      <c r="D2127" s="4" t="s">
-        <v>2238</v>
       </c>
       <c r="E2127" s="5" t="s">
         <v>229</v>
@@ -43636,16 +43633,16 @@
         <v>5</v>
       </c>
       <c r="B2128" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2128" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D2128" s="4" t="s">
         <v>2237</v>
       </c>
-      <c r="D2128" s="4" t="s">
-        <v>2238</v>
-      </c>
       <c r="E2128" s="5" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="2129" spans="1:5" x14ac:dyDescent="0.3">
@@ -43653,13 +43650,13 @@
         <v>5</v>
       </c>
       <c r="B2129" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2129" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D2129" s="4" t="s">
         <v>2237</v>
-      </c>
-      <c r="D2129" s="4" t="s">
-        <v>2238</v>
       </c>
       <c r="E2129" s="5" t="s">
         <v>44</v>
@@ -43670,16 +43667,16 @@
         <v>5</v>
       </c>
       <c r="B2130" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2130" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D2130" s="4" t="s">
         <v>2237</v>
       </c>
-      <c r="D2130" s="4" t="s">
-        <v>2238</v>
-      </c>
       <c r="E2130" s="5" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="2131" spans="1:5" x14ac:dyDescent="0.3">
@@ -43687,16 +43684,16 @@
         <v>5</v>
       </c>
       <c r="B2131" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2131" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D2131" s="4" t="s">
         <v>2237</v>
       </c>
-      <c r="D2131" s="4" t="s">
-        <v>2238</v>
-      </c>
       <c r="E2131" s="5" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="2132" spans="1:5" x14ac:dyDescent="0.3">
@@ -43704,16 +43701,16 @@
         <v>5</v>
       </c>
       <c r="B2132" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2132" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D2132" s="4" t="s">
         <v>2237</v>
       </c>
-      <c r="D2132" s="4" t="s">
-        <v>2238</v>
-      </c>
       <c r="E2132" s="5" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2133" spans="1:5" x14ac:dyDescent="0.3">
@@ -43721,16 +43718,16 @@
         <v>5</v>
       </c>
       <c r="B2133" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2133" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D2133" s="4" t="s">
         <v>2237</v>
       </c>
-      <c r="D2133" s="4" t="s">
-        <v>2238</v>
-      </c>
       <c r="E2133" s="5" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="2134" spans="1:5" x14ac:dyDescent="0.3">
@@ -43738,16 +43735,16 @@
         <v>5</v>
       </c>
       <c r="B2134" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2134" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D2134" s="4" t="s">
         <v>2237</v>
       </c>
-      <c r="D2134" s="4" t="s">
-        <v>2238</v>
-      </c>
       <c r="E2134" s="5" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="2135" spans="1:5" x14ac:dyDescent="0.3">
@@ -43755,33 +43752,33 @@
         <v>5</v>
       </c>
       <c r="B2135" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2135" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2135" s="4" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E2135" s="5" t="s">
         <v>2250</v>
       </c>
-      <c r="E2135" s="5" t="s">
+    </row>
+    <row r="2136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2136" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2136" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2136" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D2136" s="4" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E2136" s="5" t="s">
         <v>2251</v>
-      </c>
-    </row>
-    <row r="2136" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2136" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2136" s="4" t="s">
-        <v>2220</v>
-      </c>
-      <c r="C2136" s="4" t="s">
-        <v>2237</v>
-      </c>
-      <c r="D2136" s="4" t="s">
-        <v>2250</v>
-      </c>
-      <c r="E2136" s="5" t="s">
-        <v>2252</v>
       </c>
     </row>
     <row r="2137" spans="1:5" x14ac:dyDescent="0.3">
@@ -43789,13 +43786,13 @@
         <v>5</v>
       </c>
       <c r="B2137" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2137" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2137" s="4" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="E2137" s="5" t="s">
         <v>1944</v>
@@ -43806,16 +43803,16 @@
         <v>5</v>
       </c>
       <c r="B2138" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2138" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2138" s="4" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="E2138" s="5" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="2139" spans="1:5" x14ac:dyDescent="0.3">
@@ -43823,16 +43820,16 @@
         <v>5</v>
       </c>
       <c r="B2139" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2139" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2139" s="4" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="E2139" s="5" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="2140" spans="1:5" x14ac:dyDescent="0.3">
@@ -43840,33 +43837,33 @@
         <v>5</v>
       </c>
       <c r="B2140" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2140" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2140" s="4" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="E2140" s="5" t="s">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2141" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2141" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2141" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D2141" s="4" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E2141" s="5" t="s">
         <v>2255</v>
-      </c>
-    </row>
-    <row r="2141" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2141" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2141" s="4" t="s">
-        <v>2220</v>
-      </c>
-      <c r="C2141" s="4" t="s">
-        <v>2237</v>
-      </c>
-      <c r="D2141" s="4" t="s">
-        <v>2250</v>
-      </c>
-      <c r="E2141" s="5" t="s">
-        <v>2256</v>
       </c>
     </row>
     <row r="2142" spans="1:5" x14ac:dyDescent="0.3">
@@ -43874,16 +43871,16 @@
         <v>5</v>
       </c>
       <c r="B2142" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2142" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2142" s="4" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="E2142" s="5" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="2143" spans="1:5" x14ac:dyDescent="0.3">
@@ -43891,16 +43888,16 @@
         <v>5</v>
       </c>
       <c r="B2143" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2143" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2143" s="4" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="E2143" s="5" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="2144" spans="1:5" x14ac:dyDescent="0.3">
@@ -43908,33 +43905,33 @@
         <v>5</v>
       </c>
       <c r="B2144" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2144" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2144" s="4" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="E2144" s="5" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2145" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2145" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2145" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D2145" s="4" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E2145" s="5" t="s">
         <v>2259</v>
-      </c>
-    </row>
-    <row r="2145" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2145" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2145" s="4" t="s">
-        <v>2220</v>
-      </c>
-      <c r="C2145" s="4" t="s">
-        <v>2237</v>
-      </c>
-      <c r="D2145" s="4" t="s">
-        <v>2250</v>
-      </c>
-      <c r="E2145" s="5" t="s">
-        <v>2260</v>
       </c>
     </row>
     <row r="2146" spans="1:5" x14ac:dyDescent="0.3">
@@ -43942,16 +43939,16 @@
         <v>5</v>
       </c>
       <c r="B2146" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2146" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2146" s="4" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="E2146" s="5" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="2147" spans="1:5" x14ac:dyDescent="0.3">
@@ -43959,16 +43956,16 @@
         <v>5</v>
       </c>
       <c r="B2147" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2147" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2147" s="4" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="E2147" s="5" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="2148" spans="1:5" x14ac:dyDescent="0.3">
@@ -43976,16 +43973,16 @@
         <v>5</v>
       </c>
       <c r="B2148" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2148" s="12" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2148" s="12" t="s">
+        <v>2262</v>
+      </c>
+      <c r="E2148" s="3" t="s">
         <v>2263</v>
-      </c>
-      <c r="E2148" s="3" t="s">
-        <v>2264</v>
       </c>
     </row>
     <row r="2149" spans="1:5" x14ac:dyDescent="0.3">
@@ -43993,16 +43990,16 @@
         <v>5</v>
       </c>
       <c r="B2149" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2149" s="12" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2149" s="12" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="E2149" s="3" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="2150" spans="1:5" x14ac:dyDescent="0.3">
@@ -44010,16 +44007,16 @@
         <v>5</v>
       </c>
       <c r="B2150" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2150" s="12" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2150" s="12" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="E2150" s="3" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="2151" spans="1:5" x14ac:dyDescent="0.3">
@@ -44027,16 +44024,16 @@
         <v>5</v>
       </c>
       <c r="B2151" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2151" s="12" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2151" s="12" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="E2151" s="3" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="2152" spans="1:5" x14ac:dyDescent="0.3">
@@ -44044,16 +44041,16 @@
         <v>5</v>
       </c>
       <c r="B2152" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2152" s="12" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2152" s="12" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="E2152" s="3" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="2153" spans="1:5" x14ac:dyDescent="0.3">
@@ -44061,16 +44058,16 @@
         <v>5</v>
       </c>
       <c r="B2153" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2153" s="12" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2153" s="12" t="s">
+        <v>2268</v>
+      </c>
+      <c r="E2153" s="3" t="s">
         <v>2269</v>
-      </c>
-      <c r="E2153" s="3" t="s">
-        <v>2270</v>
       </c>
     </row>
     <row r="2154" spans="1:5" x14ac:dyDescent="0.3">
@@ -44078,16 +44075,16 @@
         <v>5</v>
       </c>
       <c r="B2154" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2154" s="12" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2154" s="12" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="E2154" s="3" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="2155" spans="1:5" x14ac:dyDescent="0.3">
@@ -44095,16 +44092,16 @@
         <v>5</v>
       </c>
       <c r="B2155" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2155" s="12" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2155" s="12" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="E2155" s="3" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="2156" spans="1:5" x14ac:dyDescent="0.3">
@@ -44112,16 +44109,16 @@
         <v>5</v>
       </c>
       <c r="B2156" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2156" s="12" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2156" s="12" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="E2156" s="3" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="2157" spans="1:5" x14ac:dyDescent="0.3">
@@ -44129,16 +44126,16 @@
         <v>5</v>
       </c>
       <c r="B2157" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2157" s="12" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2157" s="12" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="E2157" s="3" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="2158" spans="1:5" x14ac:dyDescent="0.3">
@@ -44146,16 +44143,16 @@
         <v>5</v>
       </c>
       <c r="B2158" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2158" s="12" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2158" s="12" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="E2158" s="3" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="2159" spans="1:5" x14ac:dyDescent="0.3">
@@ -44163,16 +44160,16 @@
         <v>5</v>
       </c>
       <c r="B2159" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2159" s="12" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2159" s="12" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="E2159" s="3" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="2160" spans="1:5" x14ac:dyDescent="0.3">
@@ -44180,16 +44177,16 @@
         <v>5</v>
       </c>
       <c r="B2160" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2160" s="12" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2160" s="12" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="E2160" s="3" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="2161" spans="1:5" x14ac:dyDescent="0.3">
@@ -44197,13 +44194,13 @@
         <v>5</v>
       </c>
       <c r="B2161" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2161" s="12" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2161" s="12" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="E2161" s="3" t="s">
         <v>628</v>
@@ -44214,16 +44211,16 @@
         <v>5</v>
       </c>
       <c r="B2162" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2162" s="12" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2162" s="12" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="E2162" s="3" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="2163" spans="1:5" x14ac:dyDescent="0.3">
@@ -44231,16 +44228,16 @@
         <v>5</v>
       </c>
       <c r="B2163" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2163" s="12" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2163" s="12" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="E2163" s="3" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="2164" spans="1:5" x14ac:dyDescent="0.3">
@@ -44248,16 +44245,16 @@
         <v>5</v>
       </c>
       <c r="B2164" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2164" s="12" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2164" s="12" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="E2164" s="3" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="2165" spans="1:5" x14ac:dyDescent="0.3">
@@ -44265,16 +44262,16 @@
         <v>5</v>
       </c>
       <c r="B2165" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2165" s="12" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2165" s="12" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="E2165" s="3" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="2166" spans="1:5" x14ac:dyDescent="0.3">
@@ -44282,16 +44279,16 @@
         <v>5</v>
       </c>
       <c r="B2166" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2166" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2166" s="4" t="s">
+        <v>2281</v>
+      </c>
+      <c r="E2166" s="5" t="s">
         <v>2282</v>
-      </c>
-      <c r="E2166" s="5" t="s">
-        <v>2283</v>
       </c>
     </row>
     <row r="2167" spans="1:5" x14ac:dyDescent="0.3">
@@ -44299,16 +44296,16 @@
         <v>5</v>
       </c>
       <c r="B2167" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2167" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2167" s="4" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="E2167" s="5" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="2168" spans="1:5" x14ac:dyDescent="0.3">
@@ -44316,16 +44313,16 @@
         <v>5</v>
       </c>
       <c r="B2168" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2168" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2168" s="4" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="E2168" s="5" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="2169" spans="1:5" x14ac:dyDescent="0.3">
@@ -44333,16 +44330,16 @@
         <v>5</v>
       </c>
       <c r="B2169" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2169" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2169" s="4" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="E2169" s="5" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="2170" spans="1:5" x14ac:dyDescent="0.3">
@@ -44350,16 +44347,16 @@
         <v>5</v>
       </c>
       <c r="B2170" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2170" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2170" s="4" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="E2170" s="5" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="2171" spans="1:5" x14ac:dyDescent="0.3">
@@ -44367,16 +44364,16 @@
         <v>5</v>
       </c>
       <c r="B2171" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2171" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2171" s="4" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="E2171" s="5" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="2172" spans="1:5" x14ac:dyDescent="0.3">
@@ -44384,13 +44381,13 @@
         <v>5</v>
       </c>
       <c r="B2172" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2172" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2172" s="4" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="E2172" s="5" t="s">
         <v>1587</v>
@@ -44401,16 +44398,16 @@
         <v>5</v>
       </c>
       <c r="B2173" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2173" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2173" s="4" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="E2173" s="5" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="2174" spans="1:5" x14ac:dyDescent="0.3">
@@ -44418,16 +44415,16 @@
         <v>5</v>
       </c>
       <c r="B2174" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2174" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2174" s="4" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="E2174" s="5" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="2175" spans="1:5" x14ac:dyDescent="0.3">
@@ -44435,16 +44432,16 @@
         <v>5</v>
       </c>
       <c r="B2175" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2175" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2175" s="4" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="E2175" s="5" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="2176" spans="1:5" x14ac:dyDescent="0.3">
@@ -44452,16 +44449,16 @@
         <v>5</v>
       </c>
       <c r="B2176" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2176" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2176" s="4" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="E2176" s="5" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="2177" spans="1:5" x14ac:dyDescent="0.3">
@@ -44469,16 +44466,16 @@
         <v>5</v>
       </c>
       <c r="B2177" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2177" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2177" s="4" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="E2177" s="5" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="2178" spans="1:5" x14ac:dyDescent="0.3">
@@ -44486,16 +44483,16 @@
         <v>5</v>
       </c>
       <c r="B2178" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2178" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2178" s="4" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="E2178" s="5" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="2179" spans="1:5" x14ac:dyDescent="0.3">
@@ -44503,33 +44500,33 @@
         <v>5</v>
       </c>
       <c r="B2179" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2179" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2179" s="4" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="E2179" s="5" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2180" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2180" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2180" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D2180" s="4" t="s">
+        <v>2281</v>
+      </c>
+      <c r="E2180" s="5" t="s">
         <v>2295</v>
-      </c>
-    </row>
-    <row r="2180" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2180" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2180" s="4" t="s">
-        <v>2220</v>
-      </c>
-      <c r="C2180" s="4" t="s">
-        <v>2237</v>
-      </c>
-      <c r="D2180" s="4" t="s">
-        <v>2282</v>
-      </c>
-      <c r="E2180" s="5" t="s">
-        <v>2296</v>
       </c>
     </row>
     <row r="2181" spans="1:5" x14ac:dyDescent="0.3">
@@ -44537,33 +44534,33 @@
         <v>5</v>
       </c>
       <c r="B2181" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2181" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2181" s="4" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="E2181" s="5" t="s">
+        <v>2296</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2182" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2182" s="4" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2182" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D2182" s="4" t="s">
+        <v>2281</v>
+      </c>
+      <c r="E2182" s="5" t="s">
         <v>2297</v>
-      </c>
-    </row>
-    <row r="2182" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2182" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2182" s="4" t="s">
-        <v>2220</v>
-      </c>
-      <c r="C2182" s="4" t="s">
-        <v>2237</v>
-      </c>
-      <c r="D2182" s="4" t="s">
-        <v>2282</v>
-      </c>
-      <c r="E2182" s="5" t="s">
-        <v>2298</v>
       </c>
     </row>
     <row r="2183" spans="1:5" x14ac:dyDescent="0.3">
@@ -44571,19 +44568,19 @@
         <v>5</v>
       </c>
       <c r="B2183" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C2183" s="4" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D2183" s="4" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="E2183" s="5" t="s">
-        <v>2299</v>
-      </c>
-    </row>
-    <row r="2184" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>2298</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2184" s="2" t="s">
         <v>5</v>
       </c>
@@ -44591,13 +44588,13 @@
         <v>28</v>
       </c>
       <c r="C2184" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2184" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2184" s="3" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="2185" spans="1:5" x14ac:dyDescent="0.3">
@@ -44608,16 +44605,16 @@
         <v>28</v>
       </c>
       <c r="C2185" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2185" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2185" s="3" t="s">
-        <v>2302</v>
-      </c>
-    </row>
-    <row r="2186" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2186" s="2" t="s">
         <v>5</v>
       </c>
@@ -44625,16 +44622,16 @@
         <v>28</v>
       </c>
       <c r="C2186" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2186" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2186" s="3" t="s">
-        <v>2303</v>
-      </c>
-    </row>
-    <row r="2187" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>2302</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2187" s="2" t="s">
         <v>5</v>
       </c>
@@ -44642,16 +44639,16 @@
         <v>28</v>
       </c>
       <c r="C2187" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2187" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2187" s="3" t="s">
-        <v>2304</v>
-      </c>
-    </row>
-    <row r="2188" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>2303</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2188" s="2" t="s">
         <v>5</v>
       </c>
@@ -44659,16 +44656,16 @@
         <v>28</v>
       </c>
       <c r="C2188" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2188" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2188" s="3" t="s">
-        <v>2305</v>
-      </c>
-    </row>
-    <row r="2189" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2189" s="2" t="s">
         <v>5</v>
       </c>
@@ -44676,16 +44673,16 @@
         <v>28</v>
       </c>
       <c r="C2189" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2189" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2189" s="3" t="s">
-        <v>2306</v>
-      </c>
-    </row>
-    <row r="2190" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>2305</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2190" s="2" t="s">
         <v>5</v>
       </c>
@@ -44693,16 +44690,16 @@
         <v>28</v>
       </c>
       <c r="C2190" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2190" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2190" s="3" t="s">
-        <v>2307</v>
-      </c>
-    </row>
-    <row r="2191" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2191" s="2" t="s">
         <v>5</v>
       </c>
@@ -44710,16 +44707,16 @@
         <v>28</v>
       </c>
       <c r="C2191" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2191" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2191" s="3" t="s">
-        <v>2308</v>
-      </c>
-    </row>
-    <row r="2192" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2192" s="2" t="s">
         <v>5</v>
       </c>
@@ -44727,16 +44724,16 @@
         <v>28</v>
       </c>
       <c r="C2192" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2192" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2192" s="3" t="s">
-        <v>2309</v>
-      </c>
-    </row>
-    <row r="2193" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2193" s="2" t="s">
         <v>5</v>
       </c>
@@ -44744,13 +44741,13 @@
         <v>28</v>
       </c>
       <c r="C2193" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2193" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2193" s="3" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="2194" spans="1:5" x14ac:dyDescent="0.3">
@@ -44761,13 +44758,13 @@
         <v>28</v>
       </c>
       <c r="C2194" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2194" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2194" s="3" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="2195" spans="1:5" x14ac:dyDescent="0.3">
@@ -44778,13 +44775,13 @@
         <v>28</v>
       </c>
       <c r="C2195" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2195" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2195" s="3" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="2196" spans="1:5" x14ac:dyDescent="0.3">
@@ -44795,13 +44792,13 @@
         <v>28</v>
       </c>
       <c r="C2196" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2196" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2196" s="3" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="2197" spans="1:5" x14ac:dyDescent="0.3">
@@ -44812,13 +44809,13 @@
         <v>28</v>
       </c>
       <c r="C2197" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2197" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2197" s="3" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="2198" spans="1:5" x14ac:dyDescent="0.3">
@@ -44829,13 +44826,13 @@
         <v>28</v>
       </c>
       <c r="C2198" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2198" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2198" s="3" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="2199" spans="1:5" x14ac:dyDescent="0.3">
@@ -44846,13 +44843,13 @@
         <v>28</v>
       </c>
       <c r="C2199" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2199" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2199" s="3" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="2200" spans="1:5" x14ac:dyDescent="0.3">
@@ -44863,13 +44860,13 @@
         <v>28</v>
       </c>
       <c r="C2200" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2200" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2200" s="3" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="2201" spans="1:5" x14ac:dyDescent="0.3">
@@ -44880,13 +44877,13 @@
         <v>28</v>
       </c>
       <c r="C2201" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2201" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2201" s="3" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="2202" spans="1:5" x14ac:dyDescent="0.3">
@@ -44897,13 +44894,13 @@
         <v>28</v>
       </c>
       <c r="C2202" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2202" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2202" s="3" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="2203" spans="1:5" x14ac:dyDescent="0.3">
@@ -44914,7 +44911,7 @@
         <v>28</v>
       </c>
       <c r="C2203" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2203" s="12" t="s">
         <v>692</v>
@@ -44931,13 +44928,13 @@
         <v>28</v>
       </c>
       <c r="C2204" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2204" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2204" s="3" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="2205" spans="1:5" x14ac:dyDescent="0.3">
@@ -44948,13 +44945,13 @@
         <v>28</v>
       </c>
       <c r="C2205" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2205" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2205" s="3" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="2206" spans="1:5" x14ac:dyDescent="0.3">
@@ -44965,7 +44962,7 @@
         <v>28</v>
       </c>
       <c r="C2206" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2206" s="12" t="s">
         <v>692</v>
@@ -44982,13 +44979,13 @@
         <v>28</v>
       </c>
       <c r="C2207" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2207" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2207" s="3" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="2208" spans="1:5" x14ac:dyDescent="0.3">
@@ -44999,13 +44996,13 @@
         <v>28</v>
       </c>
       <c r="C2208" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2208" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2208" s="3" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="2209" spans="1:5" x14ac:dyDescent="0.3">
@@ -45016,13 +45013,13 @@
         <v>28</v>
       </c>
       <c r="C2209" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2209" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2209" s="3" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="2210" spans="1:5" x14ac:dyDescent="0.3">
@@ -45033,7 +45030,7 @@
         <v>28</v>
       </c>
       <c r="C2210" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2210" s="12" t="s">
         <v>692</v>
@@ -45042,7 +45039,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2211" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2211" s="2" t="s">
         <v>5</v>
       </c>
@@ -45050,13 +45047,13 @@
         <v>28</v>
       </c>
       <c r="C2211" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2211" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2211" s="3" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="2212" spans="1:5" x14ac:dyDescent="0.3">
@@ -45067,13 +45064,13 @@
         <v>28</v>
       </c>
       <c r="C2212" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2212" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2212" s="3" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="2213" spans="1:5" x14ac:dyDescent="0.3">
@@ -45084,13 +45081,13 @@
         <v>28</v>
       </c>
       <c r="C2213" s="12" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D2213" s="12" t="s">
         <v>692</v>
       </c>
       <c r="E2213" s="3" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
     </row>
   </sheetData>
